--- a/results/interim_results/pmf_results/allsite5_FpeakErrorEstimationSummary.xlsx
+++ b/results/interim_results/pmf_results/allsite5_FpeakErrorEstimationSummary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drexel0-my.sharepoint.com/personal/lf649_drexel_edu/Documents/Desktop/pmf_02_03/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_DCC89CEE16E679C91F63398E7C68AF9BDF2253D6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26F1470C-7FB1-470F-BC17-8A6C93921DE8}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_DCC89CEE16E679491A3E59CF7FD56FDBFD745468" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AF0DECD-8E94-4BAD-90D6-5D9C76436B2B}"/>
   <bookViews>
-    <workbookView xWindow="5160" yWindow="2610" windowWidth="21795" windowHeight="11220" autoFilterDateGrouping="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5670" yWindow="975" windowWidth="21795" windowHeight="11220" autoFilterDateGrouping="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fpeak Error Estimation Summary" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
     <t>Concentration file:</t>
   </si>
   <si>
-    <t>C:\Users\lf649\Downloads\allsite_pmf.xlsx</t>
+    <t>C:\Users\lf649\OneDrive - Drexel University\allsite_pmf.xlsx</t>
   </si>
   <si>
     <t>Uncertainty file:</t>
@@ -642,7 +642,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>46056.451615069403</v>
+        <v>46056.730659294</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -703,25 +703,25 @@
         <v>0.5</v>
       </c>
       <c r="C9">
-        <v>34.339999999999698</v>
+        <v>34.459999999999603</v>
       </c>
       <c r="D9">
-        <v>2206.85</v>
+        <v>2207.2199999999998</v>
       </c>
       <c r="E9">
-        <v>1.5560640732265301</v>
+        <v>1.5612399307726501</v>
       </c>
       <c r="F9">
-        <v>30.153600000000001</v>
+        <v>30.272300000000001</v>
       </c>
       <c r="G9">
-        <v>2176.6999999999998</v>
+        <v>2176.9499999999998</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
       </c>
       <c r="I9">
-        <v>188</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
@@ -899,16 +899,16 @@
         <v>36</v>
       </c>
       <c r="B23">
-        <v>0.23433000000000001</v>
+        <v>0.23055999999999999</v>
       </c>
       <c r="C23">
-        <v>0.20333576291146899</v>
+        <v>0.20168590596640301</v>
       </c>
       <c r="D23">
-        <v>0.23650971326516201</v>
+        <v>0.23289048573396501</v>
       </c>
       <c r="E23">
-        <v>0.26729856543900599</v>
+        <v>0.26399284572938497</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
@@ -916,16 +916,16 @@
         <v>37</v>
       </c>
       <c r="B24">
-        <v>7.1820999999999996E-2</v>
+        <v>7.0897000000000002E-2</v>
       </c>
       <c r="C24">
-        <v>5.14418339916465E-2</v>
+        <v>4.8644898141583702E-2</v>
       </c>
       <c r="D24">
-        <v>7.6089067248938796E-2</v>
+        <v>7.3841558396387105E-2</v>
       </c>
       <c r="E24">
-        <v>9.7246725299768202E-2</v>
+        <v>9.4287737335197699E-2</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
@@ -933,16 +933,16 @@
         <v>38</v>
       </c>
       <c r="B25">
-        <v>4.2008999999999998E-2</v>
+        <v>4.1345E-2</v>
       </c>
       <c r="C25">
-        <v>3.5742177755241203E-2</v>
+        <v>3.53195273501134E-2</v>
       </c>
       <c r="D25">
-        <v>4.1543346781135998E-2</v>
+        <v>4.1329776924467203E-2</v>
       </c>
       <c r="E25">
-        <v>4.8778110229772298E-2</v>
+        <v>4.91349288455852E-2</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
@@ -950,16 +950,16 @@
         <v>39</v>
       </c>
       <c r="B26">
-        <v>7.2021000000000002E-2</v>
+        <v>7.0862999999999995E-2</v>
       </c>
       <c r="C26">
-        <v>6.1227130076573898E-2</v>
+        <v>5.9465610035932003E-2</v>
       </c>
       <c r="D26">
-        <v>6.9352140941810997E-2</v>
+        <v>6.9121168273031899E-2</v>
       </c>
       <c r="E26">
-        <v>7.9789485527358206E-2</v>
+        <v>7.9457723340763106E-2</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
@@ -967,16 +967,16 @@
         <v>40</v>
       </c>
       <c r="B27">
-        <v>0.16683000000000001</v>
+        <v>0.16439999999999999</v>
       </c>
       <c r="C27">
-        <v>0.107747108303553</v>
+        <v>9.8981385065741695E-2</v>
       </c>
       <c r="D27">
-        <v>0.16501369497752499</v>
+        <v>0.162673872587941</v>
       </c>
       <c r="E27">
-        <v>0.205648955168415</v>
+        <v>0.20258247505917701</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
@@ -984,16 +984,16 @@
         <v>41</v>
       </c>
       <c r="B28">
-        <v>2.1256000000000001E-2</v>
+        <v>2.0936E-2</v>
       </c>
       <c r="C28">
-        <v>1.24042775031866E-2</v>
+        <v>1.2012920428434701E-2</v>
       </c>
       <c r="D28">
-        <v>1.9142234930979201E-2</v>
+        <v>1.88289960883272E-2</v>
       </c>
       <c r="E28">
-        <v>2.6511395884647002E-2</v>
+        <v>2.6127855665504698E-2</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
@@ -1001,16 +1001,16 @@
         <v>42</v>
       </c>
       <c r="B29">
-        <v>3.5757999999999998E-2</v>
+        <v>3.517E-2</v>
       </c>
       <c r="C29">
-        <v>2.73242244312847E-2</v>
+        <v>2.65805515417522E-2</v>
       </c>
       <c r="D29">
-        <v>3.5020475189575302E-2</v>
+        <v>3.4774077395172902E-2</v>
       </c>
       <c r="E29">
-        <v>4.50718440484578E-2</v>
+        <v>4.3752080031418103E-2</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
@@ -1018,16 +1018,16 @@
         <v>43</v>
       </c>
       <c r="B30">
-        <v>1.4308E-2</v>
+        <v>1.4076E-2</v>
       </c>
       <c r="C30">
-        <v>1.12359463506059E-2</v>
+        <v>1.1080610876459399E-2</v>
       </c>
       <c r="D30">
-        <v>1.40462191617948E-2</v>
+        <v>1.3820206593811901E-2</v>
       </c>
       <c r="E30">
-        <v>1.7555745587779201E-2</v>
+        <v>1.69413561905318E-2</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
@@ -1035,16 +1035,16 @@
         <v>44</v>
       </c>
       <c r="B31">
-        <v>4.0836999999999998E-2</v>
+        <v>4.0148000000000003E-2</v>
       </c>
       <c r="C31">
-        <v>2.91621797375082E-2</v>
+        <v>2.89137614612184E-2</v>
       </c>
       <c r="D31">
-        <v>3.8851697216037699E-2</v>
+        <v>3.8196635363157698E-2</v>
       </c>
       <c r="E31">
-        <v>4.9829809885687998E-2</v>
+        <v>4.9291714093533702E-2</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
@@ -1052,16 +1052,16 @@
         <v>45</v>
       </c>
       <c r="B32">
-        <v>4.8224000000000001E-3</v>
+        <v>4.5728000000000001E-3</v>
       </c>
       <c r="C32">
         <v>0</v>
       </c>
       <c r="D32">
-        <v>1.0853433400494101E-2</v>
+        <v>1.0823244792983199E-2</v>
       </c>
       <c r="E32">
-        <v>4.7566344986095202E-2</v>
+        <v>4.5197360101626498E-2</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -1078,7 +1078,7 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>2.6790134692621599E-2</v>
+        <v>2.5830758816298899E-2</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
@@ -1086,16 +1086,16 @@
         <v>47</v>
       </c>
       <c r="B34">
-        <v>3.9461999999999997E-2</v>
+        <v>3.8837999999999998E-2</v>
       </c>
       <c r="C34">
-        <v>2.82401135941301E-2</v>
+        <v>2.4801218152891699E-2</v>
       </c>
       <c r="D34">
-        <v>3.76850805280129E-2</v>
+        <v>3.7045456652061201E-2</v>
       </c>
       <c r="E34">
-        <v>4.80575476439365E-2</v>
+        <v>4.8287585000660702E-2</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
@@ -1103,16 +1103,16 @@
         <v>48</v>
       </c>
       <c r="B35">
-        <v>5.4406999999999997E-2</v>
+        <v>5.3529E-2</v>
       </c>
       <c r="C35">
-        <v>3.3202199670747501E-2</v>
+        <v>3.23478181080653E-2</v>
       </c>
       <c r="D35">
-        <v>5.0973795259511699E-2</v>
+        <v>4.96981358916724E-2</v>
       </c>
       <c r="E35">
-        <v>7.2470667520223894E-2</v>
+        <v>6.9896313344489397E-2</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
@@ -1120,16 +1120,16 @@
         <v>49</v>
       </c>
       <c r="B36">
-        <v>4.3123000000000002E-2</v>
+        <v>4.2369999999999998E-2</v>
       </c>
       <c r="C36">
-        <v>2.0104593892970399E-2</v>
+        <v>2.1571473556470201E-2</v>
       </c>
       <c r="D36">
-        <v>3.99252134826601E-2</v>
+        <v>3.84314848123938E-2</v>
       </c>
       <c r="E36">
-        <v>5.4825271486491099E-2</v>
+        <v>5.33091855976245E-2</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
@@ -1137,16 +1137,16 @@
         <v>50</v>
       </c>
       <c r="B37">
-        <v>2.0976999999999999E-2</v>
+        <v>2.0608000000000001E-2</v>
       </c>
       <c r="C37">
-        <v>1.3857590490339E-2</v>
+        <v>1.3237494280364699E-2</v>
       </c>
       <c r="D37">
-        <v>1.9854812351002699E-2</v>
+        <v>1.9608269922011101E-2</v>
       </c>
       <c r="E37">
-        <v>2.63576649498065E-2</v>
+        <v>2.62072708932698E-2</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
@@ -1154,16 +1154,16 @@
         <v>51</v>
       </c>
       <c r="B38">
-        <v>1.6188000000000001E-2</v>
+        <v>1.5869000000000001E-2</v>
       </c>
       <c r="C38">
-        <v>1.1441554933391201E-2</v>
+        <v>1.1769023752558E-2</v>
       </c>
       <c r="D38">
-        <v>1.8123249062833299E-2</v>
+        <v>1.83525145970788E-2</v>
       </c>
       <c r="E38">
-        <v>2.5680449180722799E-2</v>
+        <v>2.4501686531443301E-2</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
@@ -1171,16 +1171,16 @@
         <v>52</v>
       </c>
       <c r="B39">
-        <v>3.8519999999999999E-2</v>
+        <v>3.7804999999999998E-2</v>
       </c>
       <c r="C39">
-        <v>2.3120592084282899E-2</v>
+        <v>2.3757759572516201E-2</v>
       </c>
       <c r="D39">
-        <v>3.6913463509545601E-2</v>
+        <v>3.6001668826461698E-2</v>
       </c>
       <c r="E39">
-        <v>5.5385526825291E-2</v>
+        <v>5.45038645970531E-2</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
@@ -1188,16 +1188,16 @@
         <v>53</v>
       </c>
       <c r="B40">
-        <v>4.6163999999999997E-2</v>
+        <v>4.5272E-2</v>
       </c>
       <c r="C40">
-        <v>3.3102668237756101E-2</v>
+        <v>3.2987416495877303E-2</v>
       </c>
       <c r="D40">
-        <v>4.8966010879751401E-2</v>
+        <v>4.8537268683970597E-2</v>
       </c>
       <c r="E40">
-        <v>6.3832722486098101E-2</v>
+        <v>6.1392231033254703E-2</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
@@ -1214,7 +1214,7 @@
         <v>0</v>
       </c>
       <c r="E41">
-        <v>2.34665684387752E-2</v>
+        <v>2.2750880959663499E-2</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
@@ -1222,16 +1222,16 @@
         <v>55</v>
       </c>
       <c r="B42">
-        <v>4.4329E-2</v>
+        <v>4.3394000000000002E-2</v>
       </c>
       <c r="C42">
-        <v>2.3658132043617702E-2</v>
+        <v>2.23511139408634E-2</v>
       </c>
       <c r="D42">
-        <v>6.7302376476896103E-2</v>
+        <v>6.5094925369163004E-2</v>
       </c>
       <c r="E42">
-        <v>0.125939655624528</v>
+        <v>0.118763229392261</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
@@ -1248,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="E43">
-        <v>1.8611732237580701E-2</v>
+        <v>1.7217040072416898E-2</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
@@ -1256,16 +1256,16 @@
         <v>57</v>
       </c>
       <c r="B44">
-        <v>0.10389</v>
+        <v>0.10196</v>
       </c>
       <c r="C44">
-        <v>4.2489857480738198E-2</v>
+        <v>4.2709490248314601E-2</v>
       </c>
       <c r="D44">
-        <v>9.2739614840767398E-2</v>
+        <v>9.0380663270018494E-2</v>
       </c>
       <c r="E44">
-        <v>0.153354975716439</v>
+        <v>0.15550527249361901</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
@@ -1273,16 +1273,16 @@
         <v>58</v>
       </c>
       <c r="B45">
-        <v>3.9442999999999998E-4</v>
+        <v>3.9723999999999998E-4</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45">
-        <v>4.7777593925154698E-4</v>
+        <v>4.20158231888198E-4</v>
       </c>
       <c r="E45">
-        <v>2.3432908685788499E-3</v>
+        <v>2.4907006301536599E-3</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
@@ -1290,16 +1290,16 @@
         <v>59</v>
       </c>
       <c r="B46">
-        <v>0.11899999999999999</v>
+        <v>0.11735</v>
       </c>
       <c r="C46">
-        <v>8.1467131259040398E-2</v>
+        <v>8.0688474386532594E-2</v>
       </c>
       <c r="D46">
-        <v>0.113482151248066</v>
+        <v>0.110205246792509</v>
       </c>
       <c r="E46">
-        <v>0.14639225172451101</v>
+        <v>0.135516294325599</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
@@ -1307,16 +1307,16 @@
         <v>60</v>
       </c>
       <c r="B47">
-        <v>3.4762999999999999E-3</v>
+        <v>3.4058999999999999E-3</v>
       </c>
       <c r="C47">
         <v>0</v>
       </c>
       <c r="D47">
-        <v>2.4087060887728498E-3</v>
+        <v>2.31683180729656E-3</v>
       </c>
       <c r="E47">
-        <v>6.1967319622095798E-3</v>
+        <v>6.1162855163303604E-3</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
@@ -1324,16 +1324,16 @@
         <v>61</v>
       </c>
       <c r="B48">
-        <v>2.8614999999999999E-3</v>
+        <v>2.9605E-3</v>
       </c>
       <c r="C48">
         <v>0</v>
       </c>
       <c r="D48">
-        <v>7.0573997534280003E-3</v>
+        <v>6.2600125141249003E-3</v>
       </c>
       <c r="E48">
-        <v>2.22011563486538E-2</v>
+        <v>1.9442851599245699E-2</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
@@ -1363,16 +1363,16 @@
         <v>36</v>
       </c>
       <c r="B52">
-        <v>0.14985999999999999</v>
+        <v>0.49782999999999999</v>
       </c>
       <c r="C52">
-        <v>0.10016345266011201</v>
+        <v>0.36562773962565198</v>
       </c>
       <c r="D52">
-        <v>0.154134868290875</v>
+        <v>0.46093988165490002</v>
       </c>
       <c r="E52">
-        <v>0.21124434612463799</v>
+        <v>0.54799537573447699</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
@@ -1380,16 +1380,16 @@
         <v>37</v>
       </c>
       <c r="B53">
-        <v>1.1495E-2</v>
+        <v>0.1464</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>0.10573129124257299</v>
       </c>
       <c r="D53">
-        <v>1.31588818800931E-2</v>
+        <v>0.14073866377555599</v>
       </c>
       <c r="E53">
-        <v>2.5603702331973201E-2</v>
+        <v>0.183768013670768</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
@@ -1397,16 +1397,16 @@
         <v>38</v>
       </c>
       <c r="B54">
-        <v>1.8634999999999999E-2</v>
+        <v>7.5898999999999994E-2</v>
       </c>
       <c r="C54">
-        <v>1.4575341527967699E-2</v>
+        <v>5.7408980174613003E-2</v>
       </c>
       <c r="D54">
-        <v>1.9217903145679699E-2</v>
+        <v>7.0785165486589099E-2</v>
       </c>
       <c r="E54">
-        <v>2.5004728431401502E-2</v>
+        <v>8.1362330722478504E-2</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
@@ -1414,16 +1414,16 @@
         <v>39</v>
       </c>
       <c r="B55">
-        <v>3.4728000000000002E-2</v>
+        <v>9.5588000000000006E-2</v>
       </c>
       <c r="C55">
-        <v>2.14419417356762E-2</v>
+        <v>6.5107816815242095E-2</v>
       </c>
       <c r="D55">
-        <v>3.4626763076063001E-2</v>
+        <v>8.8978223368627499E-2</v>
       </c>
       <c r="E55">
-        <v>5.1887748768880602E-2</v>
+        <v>0.10770983489642801</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
@@ -1431,16 +1431,16 @@
         <v>40</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>0.27723999999999999</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>0.21477238587941999</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>0.262707905543829</v>
       </c>
       <c r="E56">
-        <v>2.3321317476647199E-2</v>
+        <v>0.32102308288435799</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
@@ -1448,16 +1448,16 @@
         <v>41</v>
       </c>
       <c r="B57">
-        <v>8.1436000000000008E-3</v>
+        <v>3.4269999999999999E-3</v>
       </c>
       <c r="C57">
-        <v>2.9879052766780601E-3</v>
+        <v>1.2656653083792601E-3</v>
       </c>
       <c r="D57">
-        <v>7.5382121042336797E-3</v>
+        <v>3.5991450081945199E-3</v>
       </c>
       <c r="E57">
-        <v>1.4220572532387701E-2</v>
+        <v>1.8146089874470799E-2</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
@@ -1465,16 +1465,16 @@
         <v>42</v>
       </c>
       <c r="B58">
-        <v>2.3441E-2</v>
+        <v>3.3204999999999998E-2</v>
       </c>
       <c r="C58">
-        <v>1.4645706781991201E-2</v>
+        <v>2.06628298220424E-2</v>
       </c>
       <c r="D58">
-        <v>2.2423335524703401E-2</v>
+        <v>3.1581738906137302E-2</v>
       </c>
       <c r="E58">
-        <v>2.9912148266448099E-2</v>
+        <v>4.0455243613421801E-2</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
@@ -1482,16 +1482,16 @@
         <v>43</v>
       </c>
       <c r="B59">
-        <v>1.2367E-2</v>
+        <v>1.6362999999999999E-2</v>
       </c>
       <c r="C59">
-        <v>9.1991169078180692E-3</v>
+        <v>1.12420883297346E-2</v>
       </c>
       <c r="D59">
-        <v>1.2002739685412401E-2</v>
+        <v>1.54189326579107E-2</v>
       </c>
       <c r="E59">
-        <v>1.44175434975273E-2</v>
+        <v>1.9783304409936898E-2</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
@@ -1499,16 +1499,16 @@
         <v>44</v>
       </c>
       <c r="B60">
-        <v>4.233E-2</v>
+        <v>3.4424999999999997E-2</v>
       </c>
       <c r="C60">
-        <v>3.08700011451409E-2</v>
+        <v>2.1852177867927199E-2</v>
       </c>
       <c r="D60">
-        <v>4.1079059346395601E-2</v>
+        <v>3.3041346488386601E-2</v>
       </c>
       <c r="E60">
-        <v>5.0229439631711698E-2</v>
+        <v>4.6721683947330103E-2</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
@@ -1516,16 +1516,16 @@
         <v>45</v>
       </c>
       <c r="B61">
-        <v>6.9775000000000004E-2</v>
+        <v>0.16757</v>
       </c>
       <c r="C61">
-        <v>3.76247627143909E-2</v>
+        <v>0.11487213280315101</v>
       </c>
       <c r="D61">
-        <v>6.9115178576722405E-2</v>
+        <v>0.151045227762</v>
       </c>
       <c r="E61">
-        <v>7.7734095528100899E-2</v>
+        <v>0.18053291040160899</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
@@ -1533,16 +1533,16 @@
         <v>46</v>
       </c>
       <c r="B62">
-        <v>8.4320000000000006E-2</v>
+        <v>0.26046999999999998</v>
       </c>
       <c r="C62">
-        <v>6.9487733893760395E-2</v>
+        <v>0.229752326738277</v>
       </c>
       <c r="D62">
-        <v>8.45630323249493E-2</v>
+        <v>0.244252427417637</v>
       </c>
       <c r="E62">
-        <v>0.10111935835767399</v>
+        <v>0.25929416230178798</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
@@ -1550,16 +1550,16 @@
         <v>47</v>
       </c>
       <c r="B63">
-        <v>1.2440000000000001E-3</v>
+        <v>1.6889999999999999E-2</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>3.7789517474440699E-4</v>
       </c>
       <c r="D63">
-        <v>1.04050217185007E-3</v>
+        <v>1.53155832506952E-2</v>
       </c>
       <c r="E63">
-        <v>3.1590296752418499E-2</v>
+        <v>2.5407296384794002E-2</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
@@ -1567,16 +1567,16 @@
         <v>48</v>
       </c>
       <c r="B64">
-        <v>2.6450000000000001E-2</v>
+        <v>1.042E-2</v>
       </c>
       <c r="C64">
-        <v>1.56762762256684E-2</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>2.41423993766746E-2</v>
+        <v>1.16186523242192E-2</v>
       </c>
       <c r="E64">
-        <v>5.3274493327095197E-2</v>
+        <v>2.5001771492194701E-2</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
@@ -1584,16 +1584,16 @@
         <v>49</v>
       </c>
       <c r="B65">
-        <v>7.8543000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="C65">
-        <v>5.1664011788926899E-2</v>
+        <v>0</v>
       </c>
       <c r="D65">
-        <v>7.8252667132656203E-2</v>
+        <v>0</v>
       </c>
       <c r="E65">
-        <v>9.8233791109409996E-2</v>
+        <v>6.0346258530663199E-3</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
@@ -1601,16 +1601,16 @@
         <v>50</v>
       </c>
       <c r="B66">
-        <v>5.2142000000000001E-2</v>
+        <v>2.4830000000000001E-2</v>
       </c>
       <c r="C66">
-        <v>4.32530584812717E-2</v>
+        <v>1.8440282097068699E-2</v>
       </c>
       <c r="D66">
-        <v>5.0872008838790499E-2</v>
+        <v>2.4511643394527001E-2</v>
       </c>
       <c r="E66">
-        <v>6.17218178508799E-2</v>
+        <v>3.0739149919320901E-2</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
@@ -1618,16 +1618,16 @@
         <v>51</v>
       </c>
       <c r="B67">
-        <v>8.3049999999999999E-2</v>
+        <v>0.12512000000000001</v>
       </c>
       <c r="C67">
-        <v>6.9841038279331996E-2</v>
+        <v>0.108872504139821</v>
       </c>
       <c r="D67">
-        <v>8.2768314801538095E-2</v>
+        <v>0.116726954156259</v>
       </c>
       <c r="E67">
-        <v>8.8992032127020504E-2</v>
+        <v>0.12647224933175299</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
@@ -1635,16 +1635,16 @@
         <v>52</v>
       </c>
       <c r="B68">
-        <v>0.10982</v>
+        <v>7.5152999999999998E-2</v>
       </c>
       <c r="C68">
-        <v>8.3978519901184795E-2</v>
+        <v>5.8986632444126698E-2</v>
       </c>
       <c r="D68">
-        <v>0.10719003872383299</v>
+        <v>7.16923685006014E-2</v>
       </c>
       <c r="E68">
-        <v>0.121405021729208</v>
+        <v>9.1883893987385404E-2</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
@@ -1652,16 +1652,16 @@
         <v>53</v>
       </c>
       <c r="B69">
-        <v>0.21101</v>
+        <v>0.24984000000000001</v>
       </c>
       <c r="C69">
-        <v>0.18179704301188701</v>
+        <v>0.21505669775873301</v>
       </c>
       <c r="D69">
-        <v>0.20928987989234299</v>
+        <v>0.23490014117299601</v>
       </c>
       <c r="E69">
-        <v>0.223628742980755</v>
+        <v>0.25798863273963901</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
@@ -1669,16 +1669,16 @@
         <v>54</v>
       </c>
       <c r="B70">
-        <v>0.30753999999999998</v>
+        <v>0.31013000000000002</v>
       </c>
       <c r="C70">
-        <v>0.28031245534157501</v>
+        <v>0.26198793925155101</v>
       </c>
       <c r="D70">
-        <v>0.30485772465946698</v>
+        <v>0.29937392506786697</v>
       </c>
       <c r="E70">
-        <v>0.33846907530952097</v>
+        <v>0.34745912118066202</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
@@ -1686,16 +1686,16 @@
         <v>55</v>
       </c>
       <c r="B71">
-        <v>0.66418999999999995</v>
+        <v>0.88266999999999995</v>
       </c>
       <c r="C71">
-        <v>0.59606255923903695</v>
+        <v>0.72751002048928004</v>
       </c>
       <c r="D71">
-        <v>0.665133725375603</v>
+        <v>0.83256454149753301</v>
       </c>
       <c r="E71">
-        <v>0.75115808618192503</v>
+        <v>0.90936865802586198</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
@@ -1703,16 +1703,16 @@
         <v>56</v>
       </c>
       <c r="B72">
-        <v>3.4640999999999998E-2</v>
+        <v>0</v>
       </c>
       <c r="C72">
-        <v>2.30712852633169E-2</v>
+        <v>0</v>
       </c>
       <c r="D72">
-        <v>3.3540310192077899E-2</v>
+        <v>0</v>
       </c>
       <c r="E72">
-        <v>5.8666877016104603E-2</v>
+        <v>2.02396239479408E-3</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
@@ -1720,16 +1720,16 @@
         <v>57</v>
       </c>
       <c r="B73">
-        <v>0.38179000000000002</v>
+        <v>0.10174999999999999</v>
       </c>
       <c r="C73">
-        <v>0.29410120842194398</v>
+        <v>6.3399111547287001E-2</v>
       </c>
       <c r="D73">
-        <v>0.37109112779144898</v>
+        <v>0.104074642954412</v>
       </c>
       <c r="E73">
-        <v>0.40189613519602102</v>
+        <v>0.151228515236948</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
@@ -1737,16 +1737,16 @@
         <v>58</v>
       </c>
       <c r="B74">
-        <v>9.1301999999999996E-4</v>
+        <v>8.0424999999999993E-3</v>
       </c>
       <c r="C74">
-        <v>2.04886555116665E-4</v>
+        <v>5.0507593510641302E-3</v>
       </c>
       <c r="D74">
-        <v>1.0365729964961199E-3</v>
+        <v>8.0019744483878202E-3</v>
       </c>
       <c r="E74">
-        <v>2.1715561260599999E-3</v>
+        <v>1.20076761473971E-2</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
@@ -1754,16 +1754,16 @@
         <v>59</v>
       </c>
       <c r="B75">
-        <v>8.5428000000000001E-4</v>
+        <v>0</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75">
-        <v>7.4809189303632804E-4</v>
+        <v>0</v>
       </c>
       <c r="E75">
-        <v>3.1996224192465698E-3</v>
+        <v>1.3525604640639E-2</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
@@ -1771,16 +1771,16 @@
         <v>60</v>
       </c>
       <c r="B76">
-        <v>2.3541E-4</v>
+        <v>0</v>
       </c>
       <c r="C76">
         <v>0</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>1.7612737817841301E-3</v>
       </c>
       <c r="E76">
-        <v>4.6929459388900301E-4</v>
+        <v>5.37055993508153E-3</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
@@ -1788,16 +1788,16 @@
         <v>61</v>
       </c>
       <c r="B77">
-        <v>0</v>
+        <v>1.1776E-2</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>7.9157740730598902E-3</v>
       </c>
       <c r="D77">
-        <v>3.1736010671915298E-4</v>
+        <v>9.65753485325015E-3</v>
       </c>
       <c r="E77">
-        <v>3.1402083782528902E-3</v>
+        <v>2.1885098441164201E-2</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
@@ -1827,16 +1827,16 @@
         <v>36</v>
       </c>
       <c r="B81">
-        <v>1.7788000000000002E-2</v>
+        <v>1.8231000000000001E-2</v>
       </c>
       <c r="C81">
-        <v>1.4826727138037499E-2</v>
+        <v>1.2309425993398701E-2</v>
       </c>
       <c r="D81">
-        <v>5.4469681040830498E-2</v>
+        <v>5.0844887475636501E-2</v>
       </c>
       <c r="E81">
-        <v>8.2218739746002106E-2</v>
+        <v>8.2876496526978996E-2</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
@@ -1844,16 +1844,16 @@
         <v>37</v>
       </c>
       <c r="B82">
-        <v>9.3227000000000004E-2</v>
+        <v>9.1686000000000004E-2</v>
       </c>
       <c r="C82">
-        <v>7.7422402149428304E-2</v>
+        <v>7.59911736297951E-2</v>
       </c>
       <c r="D82">
-        <v>8.9677141392463897E-2</v>
+        <v>8.8901377476985205E-2</v>
       </c>
       <c r="E82">
-        <v>0.106946293184458</v>
+        <v>0.107926869875104</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
@@ -1861,16 +1861,16 @@
         <v>38</v>
       </c>
       <c r="B83">
-        <v>3.2680000000000001E-3</v>
+        <v>3.3322999999999998E-3</v>
       </c>
       <c r="C83">
-        <v>2.1450416884850401E-3</v>
+        <v>2.1487892775030001E-3</v>
       </c>
       <c r="D83">
-        <v>8.6776596759335807E-3</v>
+        <v>8.1169227642674292E-3</v>
       </c>
       <c r="E83">
-        <v>1.31519830034306E-2</v>
+        <v>1.2889279932688499E-2</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
@@ -1878,16 +1878,16 @@
         <v>39</v>
       </c>
       <c r="B84">
-        <v>2.8429000000000002E-3</v>
+        <v>2.9244000000000002E-3</v>
       </c>
       <c r="C84">
-        <v>2.3357800601225302E-3</v>
+        <v>1.8910141798962E-3</v>
       </c>
       <c r="D84">
-        <v>8.5977909972506702E-3</v>
+        <v>8.2698920145266308E-3</v>
       </c>
       <c r="E84">
-        <v>1.5512113572628701E-2</v>
+        <v>1.58488238379338E-2</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
@@ -1895,16 +1895,16 @@
         <v>40</v>
       </c>
       <c r="B85">
-        <v>5.7181000000000003E-2</v>
+        <v>5.6640000000000003E-2</v>
       </c>
       <c r="C85">
-        <v>4.9334153410666597E-2</v>
+        <v>4.8172269192872902E-2</v>
       </c>
       <c r="D85">
-        <v>7.2467065642694103E-2</v>
+        <v>7.0745863016412502E-2</v>
       </c>
       <c r="E85">
-        <v>9.1641895746959204E-2</v>
+        <v>9.0151562005582206E-2</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
@@ -1912,16 +1912,16 @@
         <v>41</v>
       </c>
       <c r="B86">
-        <v>4.058E-3</v>
+        <v>3.9547000000000002E-3</v>
       </c>
       <c r="C86">
         <v>0</v>
       </c>
       <c r="D86">
-        <v>2.2321876234644598E-3</v>
+        <v>2.3550612093284E-3</v>
       </c>
       <c r="E86">
-        <v>5.7730190604051504E-3</v>
+        <v>5.7417644794392399E-3</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
@@ -1935,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>1.3128671377419601E-3</v>
+        <v>1.21985218896238E-3</v>
       </c>
       <c r="E87">
-        <v>5.0473929488978799E-3</v>
+        <v>5.1781039110402197E-3</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
@@ -1952,10 +1952,10 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>6.1087107342125196E-4</v>
+        <v>5.7439306581203895E-4</v>
       </c>
       <c r="E88">
-        <v>1.92909504561727E-3</v>
+        <v>2.0821315438309999E-3</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
@@ -1969,10 +1969,10 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>4.7557744243577099E-4</v>
+        <v>4.3982304272650999E-4</v>
       </c>
       <c r="E89">
-        <v>3.8694066844688398E-3</v>
+        <v>4.74055656670471E-3</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
@@ -1980,16 +1980,16 @@
         <v>45</v>
       </c>
       <c r="B90">
-        <v>3.4808E-3</v>
+        <v>3.6608000000000001E-3</v>
       </c>
       <c r="C90">
         <v>0</v>
       </c>
       <c r="D90">
-        <v>1.6576823096817801E-2</v>
+        <v>1.5601994629628701E-2</v>
       </c>
       <c r="E90">
-        <v>3.0715937229705399E-2</v>
+        <v>2.7937013393169001E-2</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
@@ -1997,16 +1997,16 @@
         <v>46</v>
       </c>
       <c r="B91">
-        <v>2.0553999999999999E-2</v>
+        <v>2.0627E-2</v>
       </c>
       <c r="C91">
-        <v>1.40822925402145E-2</v>
+        <v>1.3003388727424899E-2</v>
       </c>
       <c r="D91">
-        <v>4.2575006438859697E-2</v>
+        <v>4.0187217054950299E-2</v>
       </c>
       <c r="E91">
-        <v>5.6255397384596798E-2</v>
+        <v>5.3204026033178801E-2</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
@@ -2014,16 +2014,16 @@
         <v>47</v>
       </c>
       <c r="B92">
-        <v>1.0638E-2</v>
+        <v>1.0432E-2</v>
       </c>
       <c r="C92">
-        <v>2.6141872696734E-3</v>
+        <v>1.67497964278755E-3</v>
       </c>
       <c r="D92">
-        <v>9.3779969811322601E-3</v>
+        <v>9.4408995757813297E-3</v>
       </c>
       <c r="E92">
-        <v>1.42473002615845E-2</v>
+        <v>1.4362937813285501E-2</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
@@ -2031,16 +2031,16 @@
         <v>48</v>
       </c>
       <c r="B93">
-        <v>1.2338E-2</v>
+        <v>1.2038999999999999E-2</v>
       </c>
       <c r="C93">
         <v>0</v>
       </c>
       <c r="D93">
-        <v>8.9384279456321703E-3</v>
+        <v>8.7896100523205904E-3</v>
       </c>
       <c r="E93">
-        <v>1.55858250598239E-2</v>
+        <v>1.44353093364989E-2</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
@@ -2048,16 +2048,16 @@
         <v>49</v>
       </c>
       <c r="B94">
-        <v>8.711E-3</v>
+        <v>8.4040999999999994E-3</v>
       </c>
       <c r="C94">
         <v>0</v>
       </c>
       <c r="D94">
-        <v>1.0797323291863699E-3</v>
+        <v>2.34308584015542E-3</v>
       </c>
       <c r="E94">
-        <v>1.31541806771358E-2</v>
+        <v>1.22681412557289E-2</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
@@ -2065,16 +2065,16 @@
         <v>50</v>
       </c>
       <c r="B95">
-        <v>8.1490999999999994E-3</v>
+        <v>7.9638999999999995E-3</v>
       </c>
       <c r="C95">
-        <v>2.5639814256367701E-3</v>
+        <v>2.3563482153635602E-3</v>
       </c>
       <c r="D95">
-        <v>6.3323970680713802E-3</v>
+        <v>6.37467330715081E-3</v>
       </c>
       <c r="E95">
-        <v>1.0638032954393299E-2</v>
+        <v>1.03061500696736E-2</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
@@ -2082,16 +2082,16 @@
         <v>51</v>
       </c>
       <c r="B96">
-        <v>9.4062E-3</v>
+        <v>9.3907999999999995E-3</v>
       </c>
       <c r="C96">
-        <v>7.78863682279567E-3</v>
+        <v>7.08345081766817E-3</v>
       </c>
       <c r="D96">
-        <v>1.7267379181917199E-2</v>
+        <v>1.63653636881817E-2</v>
       </c>
       <c r="E96">
-        <v>2.2415956090301802E-2</v>
+        <v>2.1254857244073701E-2</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="E97">
-        <v>3.8726396881032998E-3</v>
+        <v>2.9720686305313199E-3</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
@@ -2116,16 +2116,16 @@
         <v>53</v>
       </c>
       <c r="B98">
-        <v>2.8761999999999999E-2</v>
+        <v>2.8457E-2</v>
       </c>
       <c r="C98">
-        <v>2.6623147610777598E-2</v>
+        <v>2.4266307987596301E-2</v>
       </c>
       <c r="D98">
-        <v>3.9603080480139302E-2</v>
+        <v>3.7912168434118598E-2</v>
       </c>
       <c r="E98">
-        <v>4.9829949561673498E-2</v>
+        <v>4.6549808590375698E-2</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
@@ -2133,16 +2133,16 @@
         <v>54</v>
       </c>
       <c r="B99">
-        <v>0.13553000000000001</v>
+        <v>0.13319</v>
       </c>
       <c r="C99">
-        <v>0.10685346682453301</v>
+        <v>0.101164188033926</v>
       </c>
       <c r="D99">
-        <v>0.13158311948403001</v>
+        <v>0.12927709792942299</v>
       </c>
       <c r="E99">
-        <v>0.149683126706081</v>
+        <v>0.14590280363711999</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
@@ -2150,16 +2150,16 @@
         <v>55</v>
       </c>
       <c r="B100">
-        <v>0.27683999999999997</v>
+        <v>0.27252999999999999</v>
       </c>
       <c r="C100">
-        <v>0.23646182514893699</v>
+        <v>0.21351880332828599</v>
       </c>
       <c r="D100">
-        <v>0.28911931985476202</v>
+        <v>0.28463266513603602</v>
       </c>
       <c r="E100">
-        <v>0.32304371801828602</v>
+        <v>0.31826541746607501</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
@@ -2167,16 +2167,16 @@
         <v>56</v>
       </c>
       <c r="B101">
-        <v>4.9152000000000001E-2</v>
+        <v>4.8136999999999999E-2</v>
       </c>
       <c r="C101">
-        <v>2.2620343694298401E-2</v>
+        <v>2.2519500388349298E-2</v>
       </c>
       <c r="D101">
-        <v>3.7851711701442602E-2</v>
+        <v>3.9960997160736103E-2</v>
       </c>
       <c r="E101">
-        <v>6.9154588648416601E-2</v>
+        <v>6.8692209459880596E-2</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
@@ -2184,16 +2184,16 @@
         <v>57</v>
       </c>
       <c r="B102">
-        <v>3.9974999999999997E-2</v>
+        <v>3.8873999999999999E-2</v>
       </c>
       <c r="C102">
-        <v>9.7740436105545198E-3</v>
+        <v>1.1217104418002199E-2</v>
       </c>
       <c r="D102">
-        <v>2.5649697341248098E-2</v>
+        <v>2.6431960360582402E-2</v>
       </c>
       <c r="E102">
-        <v>5.0183058278950199E-2</v>
+        <v>4.8661515950257403E-2</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
@@ -2201,16 +2201,16 @@
         <v>58</v>
       </c>
       <c r="B103">
-        <v>2.0347E-3</v>
+        <v>2.0116000000000001E-3</v>
       </c>
       <c r="C103">
-        <v>1.0908404126708899E-3</v>
+        <v>1.11399489266036E-3</v>
       </c>
       <c r="D103">
-        <v>2.40408548333683E-3</v>
+        <v>2.3472499272360701E-3</v>
       </c>
       <c r="E103">
-        <v>3.9936359268895397E-3</v>
+        <v>3.8099668960330201E-3</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
@@ -2218,16 +2218,16 @@
         <v>59</v>
       </c>
       <c r="B104">
-        <v>0.14742</v>
+        <v>0.14441999999999999</v>
       </c>
       <c r="C104">
-        <v>8.3831661394552101E-2</v>
+        <v>8.8675521994454706E-2</v>
       </c>
       <c r="D104">
-        <v>0.117287411538105</v>
+        <v>0.11768023350045501</v>
       </c>
       <c r="E104">
-        <v>0.16863696708333401</v>
+        <v>0.17182859799261399</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
@@ -2244,7 +2244,7 @@
         <v>0</v>
       </c>
       <c r="E105">
-        <v>7.90383263212314E-4</v>
+        <v>9.5754296738260103E-4</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
@@ -2252,16 +2252,16 @@
         <v>61</v>
       </c>
       <c r="B106">
-        <v>0.10508000000000001</v>
+        <v>0.10304000000000001</v>
       </c>
       <c r="C106">
-        <v>6.8371952250723206E-2</v>
+        <v>6.9450992070535594E-2</v>
       </c>
       <c r="D106">
-        <v>8.9506657326629296E-2</v>
+        <v>8.8290970790034007E-2</v>
       </c>
       <c r="E106">
-        <v>0.119131162550652</v>
+        <v>0.12066882772088799</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
@@ -2291,16 +2291,16 @@
         <v>36</v>
       </c>
       <c r="B110">
-        <v>0.50748000000000004</v>
+        <v>0.14759</v>
       </c>
       <c r="C110">
-        <v>0.37071565010266999</v>
+        <v>9.3053148914197401E-2</v>
       </c>
       <c r="D110">
-        <v>0.47248930509695503</v>
+        <v>0.15185434391354799</v>
       </c>
       <c r="E110">
-        <v>0.54965526537902998</v>
+        <v>0.20402312997004701</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
@@ -2308,16 +2308,16 @@
         <v>37</v>
       </c>
       <c r="B111">
-        <v>0.14940999999999999</v>
+        <v>1.1355000000000001E-2</v>
       </c>
       <c r="C111">
-        <v>0.11059614682270801</v>
+        <v>0</v>
       </c>
       <c r="D111">
-        <v>0.144703628565403</v>
+        <v>1.3252816513134201E-2</v>
       </c>
       <c r="E111">
-        <v>0.183749615105399</v>
+        <v>2.4349496217890301E-2</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
@@ -2325,16 +2325,16 @@
         <v>38</v>
       </c>
       <c r="B112">
-        <v>7.7374999999999999E-2</v>
+        <v>1.8356999999999998E-2</v>
       </c>
       <c r="C112">
-        <v>5.8546015425406703E-2</v>
+        <v>1.38768370143234E-2</v>
       </c>
       <c r="D112">
-        <v>7.2848274786981096E-2</v>
+        <v>1.8737030322873799E-2</v>
       </c>
       <c r="E112">
-        <v>8.1513448178030704E-2</v>
+        <v>2.47141070794221E-2</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
@@ -2342,16 +2342,16 @@
         <v>39</v>
       </c>
       <c r="B113">
-        <v>9.7423999999999997E-2</v>
+        <v>3.4206E-2</v>
       </c>
       <c r="C113">
-        <v>6.7335367071421598E-2</v>
+        <v>2.14100987870115E-2</v>
       </c>
       <c r="D113">
-        <v>9.1606409788129395E-2</v>
+        <v>3.4329480289283398E-2</v>
       </c>
       <c r="E113">
-        <v>0.109910788830221</v>
+        <v>5.1850284901643597E-2</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
@@ -2359,16 +2359,16 @@
         <v>40</v>
       </c>
       <c r="B114">
-        <v>0.28255000000000002</v>
+        <v>0</v>
       </c>
       <c r="C114">
-        <v>0.22088580490620499</v>
+        <v>0</v>
       </c>
       <c r="D114">
-        <v>0.26729286337691399</v>
+        <v>0</v>
       </c>
       <c r="E114">
-        <v>0.33022490014524902</v>
+        <v>2.7827231602311001E-2</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
@@ -2376,16 +2376,16 @@
         <v>41</v>
       </c>
       <c r="B115">
-        <v>3.4978000000000001E-3</v>
+        <v>8.0359999999999997E-3</v>
       </c>
       <c r="C115">
-        <v>1.2720762794963E-3</v>
+        <v>3.1126466125203402E-3</v>
       </c>
       <c r="D115">
-        <v>3.5552738946248502E-3</v>
+        <v>7.0167985766605304E-3</v>
       </c>
       <c r="E115">
-        <v>1.92505634813122E-2</v>
+        <v>1.4219837067189999E-2</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
@@ -2393,16 +2393,16 @@
         <v>42</v>
       </c>
       <c r="B116">
-        <v>3.3820999999999997E-2</v>
+        <v>2.3085999999999999E-2</v>
       </c>
       <c r="C116">
-        <v>2.2193076057018101E-2</v>
+        <v>1.45060213961001E-2</v>
       </c>
       <c r="D116">
-        <v>3.1828098749908898E-2</v>
+        <v>2.2026713273570898E-2</v>
       </c>
       <c r="E116">
-        <v>4.05256733339922E-2</v>
+        <v>2.98123544277035E-2</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
@@ -2410,16 +2410,16 @@
         <v>43</v>
       </c>
       <c r="B117">
-        <v>1.6667999999999999E-2</v>
+        <v>1.218E-2</v>
       </c>
       <c r="C117">
-        <v>1.1402296766672201E-2</v>
+        <v>9.1146903685527907E-3</v>
       </c>
       <c r="D117">
-        <v>1.5641320860357501E-2</v>
+        <v>1.18243130792169E-2</v>
       </c>
       <c r="E117">
-        <v>2.0165454679764001E-2</v>
+        <v>1.43302014744261E-2</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
@@ -2427,16 +2427,16 @@
         <v>44</v>
       </c>
       <c r="B118">
-        <v>3.5090000000000003E-2</v>
+        <v>4.1688999999999997E-2</v>
       </c>
       <c r="C118">
-        <v>2.3263914964454499E-2</v>
+        <v>3.03507165688915E-2</v>
       </c>
       <c r="D118">
-        <v>3.3857689725934503E-2</v>
+        <v>4.0317416271777103E-2</v>
       </c>
       <c r="E118">
-        <v>4.7922008262488699E-2</v>
+        <v>5.0130486740073602E-2</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
@@ -2444,16 +2444,16 @@
         <v>45</v>
       </c>
       <c r="B119">
-        <v>0.17102000000000001</v>
+        <v>6.8831000000000003E-2</v>
       </c>
       <c r="C119">
-        <v>0.117620243622118</v>
+        <v>3.9387026593712203E-2</v>
       </c>
       <c r="D119">
-        <v>0.15782839274499399</v>
+        <v>6.8746551475692697E-2</v>
       </c>
       <c r="E119">
-        <v>0.184275852397351</v>
+        <v>7.7002111296005898E-2</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
@@ -2461,16 +2461,16 @@
         <v>46</v>
       </c>
       <c r="B120">
-        <v>0.26556999999999997</v>
+        <v>8.2998000000000002E-2</v>
       </c>
       <c r="C120">
-        <v>0.23398655415233499</v>
+        <v>6.8016628426671596E-2</v>
       </c>
       <c r="D120">
-        <v>0.24904719319523699</v>
+        <v>8.4406640340914205E-2</v>
       </c>
       <c r="E120">
-        <v>0.26577694680772801</v>
+        <v>9.99987401049207E-2</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
@@ -2478,16 +2478,16 @@
         <v>47</v>
       </c>
       <c r="B121">
-        <v>1.7194999999999998E-2</v>
+        <v>1.2246E-3</v>
       </c>
       <c r="C121">
         <v>0</v>
       </c>
       <c r="D121">
-        <v>1.5698293318868201E-2</v>
+        <v>1.2970272995151001E-3</v>
       </c>
       <c r="E121">
-        <v>2.60144194581916E-2</v>
+        <v>3.1181270904657901E-2</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
@@ -2495,16 +2495,16 @@
         <v>48</v>
       </c>
       <c r="B122">
-        <v>1.0626E-2</v>
+        <v>2.6051000000000001E-2</v>
       </c>
       <c r="C122">
-        <v>0</v>
+        <v>1.5762277308251998E-2</v>
       </c>
       <c r="D122">
-        <v>1.12031875983246E-2</v>
+        <v>2.4270835552404502E-2</v>
       </c>
       <c r="E122">
-        <v>2.68053591874945E-2</v>
+        <v>5.19080363116632E-2</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
@@ -2512,16 +2512,16 @@
         <v>49</v>
       </c>
       <c r="B123">
-        <v>0</v>
+        <v>7.7351000000000003E-2</v>
       </c>
       <c r="C123">
-        <v>0</v>
+        <v>5.0346653209714001E-2</v>
       </c>
       <c r="D123">
-        <v>0</v>
+        <v>7.6762825448533203E-2</v>
       </c>
       <c r="E123">
-        <v>5.5680006665368396E-3</v>
+        <v>9.6061501834591903E-2</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
@@ -2529,16 +2529,16 @@
         <v>50</v>
       </c>
       <c r="B124">
-        <v>2.5305000000000001E-2</v>
+        <v>5.1341999999999999E-2</v>
       </c>
       <c r="C124">
-        <v>1.8644362047706999E-2</v>
+        <v>4.2216730930427999E-2</v>
       </c>
       <c r="D124">
-        <v>2.5093217538648901E-2</v>
+        <v>5.0174414950466401E-2</v>
       </c>
       <c r="E124">
-        <v>3.1909478763689499E-2</v>
+        <v>5.8992927851272497E-2</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
@@ -2546,16 +2546,16 @@
         <v>51</v>
       </c>
       <c r="B125">
-        <v>0.12751000000000001</v>
+        <v>8.1762000000000001E-2</v>
       </c>
       <c r="C125">
-        <v>0.112260190816835</v>
+        <v>6.8751024034944805E-2</v>
       </c>
       <c r="D125">
-        <v>0.120103343717989</v>
+        <v>8.1748192540709905E-2</v>
       </c>
       <c r="E125">
-        <v>0.12839826407848501</v>
+        <v>8.7708674642641593E-2</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
@@ -2563,16 +2563,16 @@
         <v>52</v>
       </c>
       <c r="B126">
-        <v>7.6581999999999997E-2</v>
+        <v>0.10813</v>
       </c>
       <c r="C126">
-        <v>6.0370263367526003E-2</v>
+        <v>8.4122215392525096E-2</v>
       </c>
       <c r="D126">
-        <v>7.4308252775338507E-2</v>
+        <v>0.105233687928995</v>
       </c>
       <c r="E126">
-        <v>9.3549612639742402E-2</v>
+        <v>0.119389883333246</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
@@ -2580,16 +2580,16 @@
         <v>53</v>
       </c>
       <c r="B127">
-        <v>0.25463000000000002</v>
+        <v>0.20774999999999999</v>
       </c>
       <c r="C127">
-        <v>0.22217823051569199</v>
+        <v>0.17922307720457401</v>
       </c>
       <c r="D127">
-        <v>0.242097697396807</v>
+        <v>0.20611855057318801</v>
       </c>
       <c r="E127">
-        <v>0.2624880529177</v>
+        <v>0.221014153628149</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
@@ -2597,16 +2597,16 @@
         <v>54</v>
       </c>
       <c r="B128">
-        <v>0.31607000000000002</v>
+        <v>0.30264000000000002</v>
       </c>
       <c r="C128">
-        <v>0.26692926361685798</v>
+        <v>0.27242078135695702</v>
       </c>
       <c r="D128">
-        <v>0.30314360933419199</v>
+        <v>0.29996803775882502</v>
       </c>
       <c r="E128">
-        <v>0.35680963886273798</v>
+        <v>0.334915721991768</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
@@ -2614,16 +2614,16 @@
         <v>55</v>
       </c>
       <c r="B129">
-        <v>0.89959999999999996</v>
+        <v>0.65378999999999998</v>
       </c>
       <c r="C129">
-        <v>0.73646656969532498</v>
+        <v>0.58404866273979505</v>
       </c>
       <c r="D129">
-        <v>0.84311310230272496</v>
+        <v>0.65479543227798198</v>
       </c>
       <c r="E129">
-        <v>0.92485151779546904</v>
+        <v>0.75141155553411698</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
@@ -2631,16 +2631,16 @@
         <v>56</v>
       </c>
       <c r="B130">
-        <v>0</v>
+        <v>3.4118000000000002E-2</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>2.2739508231045601E-2</v>
       </c>
       <c r="D130">
-        <v>0</v>
+        <v>3.3054571131182799E-2</v>
       </c>
       <c r="E130">
-        <v>0</v>
+        <v>6.03354302073612E-2</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
@@ -2648,16 +2648,16 @@
         <v>57</v>
       </c>
       <c r="B131">
-        <v>0.10372000000000001</v>
+        <v>0.37597000000000003</v>
       </c>
       <c r="C131">
-        <v>6.8101127371213405E-2</v>
+        <v>0.297296659656207</v>
       </c>
       <c r="D131">
-        <v>0.108044119568633</v>
+        <v>0.36444579983681502</v>
       </c>
       <c r="E131">
-        <v>0.15555750744109401</v>
+        <v>0.40220384413001598</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
@@ -2665,16 +2665,16 @@
         <v>58</v>
       </c>
       <c r="B132">
-        <v>8.1948000000000003E-3</v>
+        <v>8.9696000000000003E-4</v>
       </c>
       <c r="C132">
-        <v>5.3204235405127998E-3</v>
+        <v>1.8900091031231301E-4</v>
       </c>
       <c r="D132">
-        <v>7.8905519766549904E-3</v>
+        <v>1.02845823149316E-3</v>
       </c>
       <c r="E132">
-        <v>1.2174257680339201E-2</v>
+        <v>2.1142734806620499E-3</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
@@ -2682,16 +2682,16 @@
         <v>59</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>8.4060000000000005E-4</v>
       </c>
       <c r="C133">
         <v>0</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>7.8720559340239604E-4</v>
       </c>
       <c r="E133">
-        <v>9.4487029163835504E-3</v>
+        <v>3.14875963499494E-3</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.2">
@@ -2699,16 +2699,16 @@
         <v>60</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>2.3819999999999999E-4</v>
       </c>
       <c r="C134">
         <v>0</v>
       </c>
       <c r="D134">
-        <v>1.8501383313566299E-3</v>
+        <v>0</v>
       </c>
       <c r="E134">
-        <v>5.80496146535763E-3</v>
+        <v>5.3637582813045902E-4</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.2">
@@ -2716,16 +2716,16 @@
         <v>61</v>
       </c>
       <c r="B135">
-        <v>1.2070000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="C135">
-        <v>7.5654660061481704E-3</v>
+        <v>0</v>
       </c>
       <c r="D135">
-        <v>9.79048109238502E-3</v>
+        <v>6.0103606629487204E-4</v>
       </c>
       <c r="E135">
-        <v>2.2266616740758201E-2</v>
+        <v>3.481514406676E-3</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.2">
@@ -2755,16 +2755,16 @@
         <v>36</v>
       </c>
       <c r="B139">
-        <v>0.10165</v>
+        <v>0.10014000000000001</v>
       </c>
       <c r="C139">
-        <v>7.1044134759279898E-2</v>
+        <v>7.8351260951475502E-2</v>
       </c>
       <c r="D139">
-        <v>0.107343462604629</v>
+        <v>0.10688316369074501</v>
       </c>
       <c r="E139">
-        <v>0.14630911241662001</v>
+        <v>0.149317485189399</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.2">
@@ -2772,16 +2772,16 @@
         <v>37</v>
       </c>
       <c r="B140">
-        <v>6.1929999999999999E-2</v>
+        <v>6.0920000000000002E-2</v>
       </c>
       <c r="C140">
-        <v>3.92407942345252E-2</v>
+        <v>3.5061555407812299E-2</v>
       </c>
       <c r="D140">
-        <v>6.8187491517629997E-2</v>
+        <v>6.5672824858144102E-2</v>
       </c>
       <c r="E140">
-        <v>0.10200996879027301</v>
+        <v>9.3479128403121794E-2</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.2">
@@ -2789,16 +2789,16 @@
         <v>38</v>
       </c>
       <c r="B141">
-        <v>1.1726E-2</v>
+        <v>1.1540999999999999E-2</v>
       </c>
       <c r="C141">
-        <v>6.5636366112469102E-3</v>
+        <v>6.7826292892851203E-3</v>
       </c>
       <c r="D141">
-        <v>1.2148677338955E-2</v>
+        <v>1.2131641787337701E-2</v>
       </c>
       <c r="E141">
-        <v>1.8210167714821701E-2</v>
+        <v>1.7755962549764501E-2</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.2">
@@ -2806,16 +2806,16 @@
         <v>39</v>
       </c>
       <c r="B142">
-        <v>1.3818E-2</v>
+        <v>1.3582E-2</v>
       </c>
       <c r="C142">
-        <v>8.4532213016146E-3</v>
+        <v>8.5487126455306307E-3</v>
       </c>
       <c r="D142">
-        <v>1.5856564434446899E-2</v>
+        <v>1.60514903998023E-2</v>
       </c>
       <c r="E142">
-        <v>2.62186268116778E-2</v>
+        <v>2.68386680387902E-2</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.2">
@@ -2823,16 +2823,16 @@
         <v>40</v>
       </c>
       <c r="B143">
-        <v>9.7361000000000003E-2</v>
+        <v>9.5635999999999999E-2</v>
       </c>
       <c r="C143">
-        <v>5.9051431579440899E-2</v>
+        <v>5.9773833498139299E-2</v>
       </c>
       <c r="D143">
-        <v>0.106052868814211</v>
+        <v>0.104008997287465</v>
       </c>
       <c r="E143">
-        <v>0.15177438650591901</v>
+        <v>0.151786299758775</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.2">
@@ -2840,16 +2840,16 @@
         <v>41</v>
       </c>
       <c r="B144">
-        <v>2.0078000000000001E-3</v>
+        <v>1.9530999999999999E-3</v>
       </c>
       <c r="C144">
         <v>0</v>
       </c>
       <c r="D144">
-        <v>3.3822508190830798E-3</v>
+        <v>3.0239131835346198E-3</v>
       </c>
       <c r="E144">
-        <v>8.8757559242368493E-3</v>
+        <v>8.5753362054511294E-3</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.2">
@@ -2866,7 +2866,7 @@
         <v>0</v>
       </c>
       <c r="E145">
-        <v>3.7566604443184299E-3</v>
+        <v>4.0294983784953404E-3</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.2">
@@ -2883,7 +2883,7 @@
         <v>0</v>
       </c>
       <c r="E146">
-        <v>1.6143035717348501E-3</v>
+        <v>1.57360411592056E-3</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
@@ -2897,10 +2897,10 @@
         <v>0</v>
       </c>
       <c r="D147">
-        <v>1.94215709928829E-3</v>
+        <v>1.96226140014412E-3</v>
       </c>
       <c r="E147">
-        <v>7.8088262575073996E-3</v>
+        <v>8.2108723249274106E-3</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
@@ -2908,16 +2908,16 @@
         <v>45</v>
       </c>
       <c r="B148">
-        <v>3.4265999999999998E-2</v>
+        <v>3.4055000000000002E-2</v>
       </c>
       <c r="C148">
         <v>0</v>
       </c>
       <c r="D148">
-        <v>2.4870937389486501E-2</v>
+        <v>2.65249723181143E-2</v>
       </c>
       <c r="E148">
-        <v>6.2927738003000097E-2</v>
+        <v>6.4194355757508106E-2</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.2">
@@ -2925,16 +2925,16 @@
         <v>46</v>
       </c>
       <c r="B149">
-        <v>5.1976000000000001E-2</v>
+        <v>5.1292999999999998E-2</v>
       </c>
       <c r="C149">
         <v>0</v>
       </c>
       <c r="D149">
-        <v>5.4045501262660001E-2</v>
+        <v>5.6700703555215601E-2</v>
       </c>
       <c r="E149">
-        <v>7.9293154297516294E-2</v>
+        <v>8.0053560201284596E-2</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.2">
@@ -2942,16 +2942,16 @@
         <v>47</v>
       </c>
       <c r="B150">
-        <v>6.8998999999999996E-3</v>
+        <v>6.7786000000000001E-3</v>
       </c>
       <c r="C150">
-        <v>3.2521164720502601E-4</v>
+        <v>3.0518813547110999E-4</v>
       </c>
       <c r="D150">
-        <v>9.9472399882603695E-3</v>
+        <v>9.4806207499115395E-3</v>
       </c>
       <c r="E150">
-        <v>2.7899488114099799E-2</v>
+        <v>2.5515412676379901E-2</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
@@ -2968,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="E151">
-        <v>2.4789667406152301E-2</v>
+        <v>2.54026920031768E-2</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.2">
@@ -2982,10 +2982,10 @@
         <v>0</v>
       </c>
       <c r="D152">
-        <v>5.7402433331566203E-3</v>
+        <v>5.2084256138867999E-3</v>
       </c>
       <c r="E152">
-        <v>2.71193151082962E-2</v>
+        <v>2.3344510748921202E-2</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.2">
@@ -2993,16 +2993,16 @@
         <v>50</v>
       </c>
       <c r="B153">
-        <v>7.9944000000000005E-3</v>
+        <v>7.8732000000000003E-3</v>
       </c>
       <c r="C153">
-        <v>6.37433556288891E-3</v>
+        <v>6.27665067400249E-3</v>
       </c>
       <c r="D153">
-        <v>1.14424971608317E-2</v>
+        <v>1.1126502368391401E-2</v>
       </c>
       <c r="E153">
-        <v>2.0560329906828999E-2</v>
+        <v>1.8913620839302699E-2</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.2">
@@ -3010,16 +3010,16 @@
         <v>51</v>
       </c>
       <c r="B154">
-        <v>2.6178E-2</v>
+        <v>2.5815999999999999E-2</v>
       </c>
       <c r="C154">
-        <v>1.0176744645117201E-2</v>
+        <v>1.050403965726E-2</v>
       </c>
       <c r="D154">
-        <v>2.9204152231922E-2</v>
+        <v>3.02139808377049E-2</v>
       </c>
       <c r="E154">
-        <v>4.1117760942179497E-2</v>
+        <v>4.1551092738852199E-2</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.2">
@@ -3027,16 +3027,16 @@
         <v>52</v>
       </c>
       <c r="B155">
-        <v>1.0522000000000001E-3</v>
+        <v>1.0671999999999999E-3</v>
       </c>
       <c r="C155">
         <v>0</v>
       </c>
       <c r="D155">
-        <v>5.1685432141342202E-3</v>
+        <v>5.6563898502325002E-3</v>
       </c>
       <c r="E155">
-        <v>1.6893290419269898E-2</v>
+        <v>1.74521848163765E-2</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.2">
@@ -3044,16 +3044,16 @@
         <v>53</v>
       </c>
       <c r="B156">
-        <v>5.2308E-2</v>
+        <v>5.1596000000000003E-2</v>
       </c>
       <c r="C156">
-        <v>2.80122820405991E-2</v>
+        <v>2.73459315267028E-2</v>
       </c>
       <c r="D156">
-        <v>6.0790472036665197E-2</v>
+        <v>6.2839741165969604E-2</v>
       </c>
       <c r="E156">
-        <v>8.8625850786269597E-2</v>
+        <v>8.7052907294456305E-2</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.2">
@@ -3061,16 +3061,16 @@
         <v>54</v>
       </c>
       <c r="B157">
-        <v>5.8058999999999999E-2</v>
+        <v>5.7155999999999998E-2</v>
       </c>
       <c r="C157">
-        <v>9.5884737373934104E-3</v>
+        <v>9.9609192057641405E-3</v>
       </c>
       <c r="D157">
-        <v>7.8409461733050898E-2</v>
+        <v>7.6868567366105894E-2</v>
       </c>
       <c r="E157">
-        <v>0.11173115900733201</v>
+        <v>0.107526072541424</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.2">
@@ -3078,16 +3078,16 @@
         <v>55</v>
       </c>
       <c r="B158">
-        <v>0.26400000000000001</v>
+        <v>0.26016</v>
       </c>
       <c r="C158">
-        <v>0.18374057688821399</v>
+        <v>0.183890919357487</v>
       </c>
       <c r="D158">
-        <v>0.30199858147192099</v>
+        <v>0.298879829639629</v>
       </c>
       <c r="E158">
-        <v>0.37394684479738999</v>
+        <v>0.36024903600104902</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.2">
@@ -3095,16 +3095,16 @@
         <v>56</v>
       </c>
       <c r="B159">
-        <v>6.1520999999999999E-2</v>
+        <v>6.0533000000000003E-2</v>
       </c>
       <c r="C159">
-        <v>2.4722530833182901E-2</v>
+        <v>2.6108291581369202E-2</v>
       </c>
       <c r="D159">
-        <v>7.0958574761318394E-2</v>
+        <v>6.6493957535860695E-2</v>
       </c>
       <c r="E159">
-        <v>0.112077585365415</v>
+        <v>0.11426239185999899</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.2">
@@ -3118,10 +3118,10 @@
         <v>0</v>
       </c>
       <c r="D160">
-        <v>1.7090297724082101E-2</v>
+        <v>1.7729899612627699E-2</v>
       </c>
       <c r="E160">
-        <v>5.7802483830983499E-2</v>
+        <v>5.6479942272048202E-2</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.2">
@@ -3129,16 +3129,16 @@
         <v>58</v>
       </c>
       <c r="B161">
-        <v>3.9436000000000002E-3</v>
+        <v>3.8784000000000002E-3</v>
       </c>
       <c r="C161">
-        <v>8.8393110736128904E-4</v>
+        <v>7.7740464848622E-4</v>
       </c>
       <c r="D161">
-        <v>3.8761826041844899E-3</v>
+        <v>3.85100805822972E-3</v>
       </c>
       <c r="E161">
-        <v>6.3132168480059302E-3</v>
+        <v>5.8680963219402502E-3</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.2">
@@ -3146,16 +3146,16 @@
         <v>59</v>
       </c>
       <c r="B162">
-        <v>9.6016000000000001E-3</v>
+        <v>9.3220000000000004E-3</v>
       </c>
       <c r="C162">
         <v>0</v>
       </c>
       <c r="D162">
-        <v>1.4293206044627801E-2</v>
+        <v>1.24690018565071E-2</v>
       </c>
       <c r="E162">
-        <v>0.111602660799846</v>
+        <v>0.11015239753070701</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.2">
@@ -3163,16 +3163,16 @@
         <v>60</v>
       </c>
       <c r="B163">
-        <v>1.6289000000000001E-2</v>
+        <v>1.6041E-2</v>
       </c>
       <c r="C163">
-        <v>1.0721637561306801E-2</v>
+        <v>1.01792976448879E-2</v>
       </c>
       <c r="D163">
-        <v>1.75334116822707E-2</v>
+        <v>1.7391628949183301E-2</v>
       </c>
       <c r="E163">
-        <v>3.3069807777574303E-2</v>
+        <v>3.3173267209029002E-2</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.2">
@@ -3189,7 +3189,7 @@
         <v>0</v>
       </c>
       <c r="E164">
-        <v>2.39983328626013E-2</v>
+        <v>2.3551612590954701E-2</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.2">
@@ -3219,16 +3219,16 @@
         <v>36</v>
       </c>
       <c r="B168">
-        <v>23.3832302093506</v>
+        <v>23.348741531372099</v>
       </c>
       <c r="C168">
-        <v>19.665276039453801</v>
+        <v>20.021887197411999</v>
       </c>
       <c r="D168">
-        <v>23.266280319629701</v>
+        <v>23.313666456044601</v>
       </c>
       <c r="E168">
-        <v>26.706593381755699</v>
+        <v>26.922069233404201</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.2">
@@ -3236,16 +3236,16 @@
         <v>37</v>
       </c>
       <c r="B169">
-        <v>19.1255283355713</v>
+        <v>19.1073322296143</v>
       </c>
       <c r="C169">
-        <v>12.208550671805501</v>
+        <v>11.969197922737999</v>
       </c>
       <c r="D169">
-        <v>19.475242929230301</v>
+        <v>19.443401783968</v>
       </c>
       <c r="E169">
-        <v>24.9188048990681</v>
+        <v>25.2141400530762</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.2">
@@ -3253,16 +3253,16 @@
         <v>38</v>
       </c>
       <c r="B170">
-        <v>27.572746276855501</v>
+        <v>27.542413711547901</v>
       </c>
       <c r="C170">
-        <v>23.103145919498701</v>
+        <v>23.3094639602844</v>
       </c>
       <c r="D170">
-        <v>27.163937425294701</v>
+        <v>27.282116032330102</v>
       </c>
       <c r="E170">
-        <v>32.069287244517199</v>
+        <v>32.1721769212377</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.2">
@@ -3270,16 +3270,16 @@
         <v>39</v>
       </c>
       <c r="B171">
-        <v>32.731925964355497</v>
+        <v>32.687534332275398</v>
       </c>
       <c r="C171">
-        <v>27.460226538189399</v>
+        <v>27.661153953462399</v>
       </c>
       <c r="D171">
-        <v>31.641434330748702</v>
+        <v>31.906168399872499</v>
       </c>
       <c r="E171">
-        <v>35.727308679751999</v>
+        <v>36.005453360053501</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.2">
@@ -3287,16 +3287,16 @@
         <v>40</v>
       </c>
       <c r="B172">
-        <v>28.001768112182599</v>
+        <v>27.9700031280518</v>
       </c>
       <c r="C172">
-        <v>16.271478470030601</v>
+        <v>15.621990192584001</v>
       </c>
       <c r="D172">
-        <v>27.566282682777899</v>
+        <v>27.635284770384899</v>
       </c>
       <c r="E172">
-        <v>35.893128041847298</v>
+        <v>35.355063882969702</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.2">
@@ -3304,16 +3304,16 @@
         <v>41</v>
       </c>
       <c r="B173">
-        <v>55.430652618408203</v>
+        <v>55.366008758544901</v>
       </c>
       <c r="C173">
-        <v>30.496920512152801</v>
+        <v>30.86334629601</v>
       </c>
       <c r="D173">
-        <v>49.378587010639599</v>
+        <v>49.631066110617802</v>
       </c>
       <c r="E173">
-        <v>58.987221325710898</v>
+        <v>59.019437963214799</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.2">
@@ -3321,16 +3321,16 @@
         <v>42</v>
       </c>
       <c r="B174">
-        <v>39.084800720214801</v>
+        <v>39.028694152832003</v>
       </c>
       <c r="C174">
-        <v>30.1175061227678</v>
+        <v>29.9157597214076</v>
       </c>
       <c r="D174">
-        <v>38.101802529896801</v>
+        <v>38.5048302052327</v>
       </c>
       <c r="E174">
-        <v>47.3622596304307</v>
+        <v>47.207098223888202</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.2">
@@ -3338,16 +3338,16 @@
         <v>43</v>
       </c>
       <c r="B175">
-        <v>33.646373748779297</v>
+        <v>33.602798461914098</v>
       </c>
       <c r="C175">
-        <v>25.7546206233969</v>
+        <v>26.195481894149399</v>
       </c>
       <c r="D175">
-        <v>32.552094012584902</v>
+        <v>32.702851770641601</v>
       </c>
       <c r="E175">
-        <v>40.858824465191603</v>
+        <v>40.870244553178203</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.2">
@@ -3355,16 +3355,16 @@
         <v>44</v>
       </c>
       <c r="B176">
-        <v>34.886669158935497</v>
+        <v>34.819126129150398</v>
       </c>
       <c r="C176">
-        <v>24.408244971397899</v>
+        <v>24.924061443922501</v>
       </c>
       <c r="D176">
-        <v>32.889460783243301</v>
+        <v>32.896076020366699</v>
       </c>
       <c r="E176">
-        <v>42.068106255548997</v>
+        <v>42.838103336848498</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.2">
@@ -3372,16 +3372,16 @@
         <v>45</v>
       </c>
       <c r="B177">
-        <v>1.80223441123962</v>
+        <v>1.7472231388092001</v>
       </c>
       <c r="C177">
         <v>0</v>
       </c>
       <c r="D177">
-        <v>4.0651668469694098</v>
+        <v>4.2038905493962497</v>
       </c>
       <c r="E177">
-        <v>18.063023966803701</v>
+        <v>17.726797918482902</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.2">
@@ -3398,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="E178">
-        <v>6.1461505947079997</v>
+        <v>5.8289065013169399</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.2">
@@ -3406,16 +3406,16 @@
         <v>47</v>
       </c>
       <c r="B179">
-        <v>52.121994018554702</v>
+        <v>52.047695159912102</v>
       </c>
       <c r="C179">
-        <v>36.591625308674402</v>
+        <v>34.049026250711101</v>
       </c>
       <c r="D179">
-        <v>48.088153054772199</v>
+        <v>48.673595990007797</v>
       </c>
       <c r="E179">
-        <v>57.978759000894698</v>
+        <v>58.622735871210999</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.2">
@@ -3423,16 +3423,16 @@
         <v>48</v>
       </c>
       <c r="B180">
-        <v>52.308391571044901</v>
+        <v>52.221500396728501</v>
       </c>
       <c r="C180">
-        <v>34.521514464457901</v>
+        <v>34.149220821205503</v>
       </c>
       <c r="D180">
-        <v>48.851911814603</v>
+        <v>48.9868265657271</v>
       </c>
       <c r="E180">
-        <v>60.855884756151603</v>
+        <v>60.2813541800395</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.2">
@@ -3440,16 +3440,16 @@
         <v>49</v>
       </c>
       <c r="B181">
-        <v>33.564174652099602</v>
+        <v>33.443771362304702</v>
       </c>
       <c r="C181">
-        <v>16.1191098272209</v>
+        <v>17.395169743533199</v>
       </c>
       <c r="D181">
-        <v>30.701711250860502</v>
+        <v>30.365044421278899</v>
       </c>
       <c r="E181">
-        <v>43.459580743332701</v>
+        <v>42.813269173028601</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.2">
@@ -3457,16 +3457,16 @@
         <v>50</v>
       </c>
       <c r="B182">
-        <v>18.791954040527301</v>
+        <v>18.712486267089801</v>
       </c>
       <c r="C182">
-        <v>11.838584268264</v>
+        <v>11.731196153687099</v>
       </c>
       <c r="D182">
-        <v>17.278788211247399</v>
+        <v>17.408686405781999</v>
       </c>
       <c r="E182">
-        <v>23.838473965231199</v>
+        <v>23.452969587528401</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.2">
@@ -3474,16 +3474,16 @@
         <v>51</v>
       </c>
       <c r="B183">
-        <v>6.5469498634338397</v>
+        <v>6.5152897834777797</v>
       </c>
       <c r="C183">
-        <v>4.2672479443101903</v>
+        <v>4.42082740497119</v>
       </c>
       <c r="D183">
-        <v>6.8540001001247299</v>
+        <v>7.0195388348158696</v>
       </c>
       <c r="E183">
-        <v>10.0801482592922</v>
+        <v>9.6107920826019697</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.2">
@@ -3491,16 +3491,16 @@
         <v>52</v>
       </c>
       <c r="B184">
-        <v>17.246515274047901</v>
+        <v>17.185661315918001</v>
       </c>
       <c r="C184">
-        <v>9.8313898875188706</v>
+        <v>10.193329924759</v>
       </c>
       <c r="D184">
-        <v>16.254247060007401</v>
+        <v>16.1778169429464</v>
       </c>
       <c r="E184">
-        <v>26.1377990643442</v>
+        <v>26.941129161402198</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.2">
@@ -3508,16 +3508,16 @@
         <v>53</v>
       </c>
       <c r="B185">
-        <v>8.1537513732910192</v>
+        <v>8.1123638153076207</v>
       </c>
       <c r="C185">
-        <v>5.5533490176714997</v>
+        <v>5.5425657543114699</v>
       </c>
       <c r="D185">
-        <v>8.2610011676753192</v>
+        <v>8.2663505675901394</v>
       </c>
       <c r="E185">
-        <v>11.2159190617544</v>
+        <v>11.115377041108699</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.2">
@@ -3534,7 +3534,7 @@
         <v>0</v>
       </c>
       <c r="E186">
-        <v>2.7618044122942602</v>
+        <v>2.74538108855455</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.2">
@@ -3542,16 +3542,16 @@
         <v>55</v>
       </c>
       <c r="B187">
-        <v>2.5235321521759002</v>
+        <v>2.4891426563262899</v>
       </c>
       <c r="C187">
-        <v>1.09344237299528</v>
+        <v>1.0767796982209401</v>
       </c>
       <c r="D187">
-        <v>3.11202421122201</v>
+        <v>3.06967580340774</v>
       </c>
       <c r="E187">
-        <v>5.76206795855372</v>
+        <v>5.5326651194587901</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.2">
@@ -3559,7 +3559,7 @@
         <v>56</v>
       </c>
       <c r="B188">
-        <v>0.22666272521019001</v>
+        <v>7.7477671205997495E-2</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -3568,7 +3568,7 @@
         <v>0</v>
       </c>
       <c r="E188">
-        <v>13.3847279075635</v>
+        <v>13.236782750672599</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.2">
@@ -3576,16 +3576,16 @@
         <v>57</v>
       </c>
       <c r="B189">
-        <v>16.8649597167969</v>
+        <v>16.7802219390869</v>
       </c>
       <c r="C189">
-        <v>6.7305660972841199</v>
+        <v>7.1915962226009098</v>
       </c>
       <c r="D189">
-        <v>14.9436934754916</v>
+        <v>14.7892223521263</v>
       </c>
       <c r="E189">
-        <v>25.386791167089999</v>
+        <v>26.702847710572499</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.2">
@@ -3593,16 +3593,16 @@
         <v>58</v>
       </c>
       <c r="B190">
-        <v>2.87548160552979</v>
+        <v>2.8652396202087398</v>
       </c>
       <c r="C190">
         <v>0</v>
       </c>
       <c r="D190">
-        <v>2.8655539893470299</v>
+        <v>2.6421989250023001</v>
       </c>
       <c r="E190">
-        <v>14.5180283416985</v>
+        <v>16.459160146337101</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.2">
@@ -3610,16 +3610,16 @@
         <v>59</v>
       </c>
       <c r="B191">
-        <v>43.398204803466797</v>
+        <v>43.402370452880902</v>
       </c>
       <c r="C191">
-        <v>26.130722261464499</v>
+        <v>25.128230534328502</v>
       </c>
       <c r="D191">
-        <v>43.665244291226998</v>
+        <v>43.103940338398701</v>
       </c>
       <c r="E191">
-        <v>57.500386323853597</v>
+        <v>55.150214818366202</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.2">
@@ -3627,16 +3627,16 @@
         <v>60</v>
       </c>
       <c r="B192">
-        <v>19.8954887390137</v>
+        <v>19.673906326293899</v>
       </c>
       <c r="C192">
         <v>0</v>
       </c>
       <c r="D192">
-        <v>10.767446530042999</v>
+        <v>10.5103358880369</v>
       </c>
       <c r="E192">
-        <v>33.624644257084903</v>
+        <v>35.776235904329297</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.2">
@@ -3644,16 +3644,16 @@
         <v>61</v>
       </c>
       <c r="B193">
-        <v>3.3584139347076398</v>
+        <v>3.3745105266571001</v>
       </c>
       <c r="C193">
         <v>0</v>
       </c>
       <c r="D193">
-        <v>6.3821365213568297</v>
+        <v>5.9051046392807001</v>
       </c>
       <c r="E193">
-        <v>20.022304758028401</v>
+        <v>17.259280760365101</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.2">
@@ -3683,16 +3683,16 @@
         <v>36</v>
       </c>
       <c r="B197">
-        <v>14.813480377197299</v>
+        <v>47.499473571777301</v>
       </c>
       <c r="C197">
-        <v>10.067914887212099</v>
+        <v>37.315240956846601</v>
       </c>
       <c r="D197">
-        <v>14.9209318948326</v>
+        <v>45.9350553995979</v>
       </c>
       <c r="E197">
-        <v>20.935862711278901</v>
+        <v>53.198233813392001</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.2">
@@ -3700,16 +3700,16 @@
         <v>37</v>
       </c>
       <c r="B198">
-        <v>3.43089771270752</v>
+        <v>35.248367309570298</v>
       </c>
       <c r="C198">
-        <v>0</v>
+        <v>29.555484358876502</v>
       </c>
       <c r="D198">
-        <v>3.3964055012077501</v>
+        <v>36.404023557463901</v>
       </c>
       <c r="E198">
-        <v>6.3492813135272703</v>
+        <v>45.064849153486001</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.2">
@@ -3717,16 +3717,16 @@
         <v>38</v>
       </c>
       <c r="B199">
-        <v>12.249279975891101</v>
+        <v>47.8987846374512</v>
       </c>
       <c r="C199">
-        <v>9.3968101713147494</v>
+        <v>39.8414565967554</v>
       </c>
       <c r="D199">
-        <v>12.440306963997299</v>
+        <v>46.834326532148999</v>
       </c>
       <c r="E199">
-        <v>16.712822204867901</v>
+        <v>52.076724902854103</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.2">
@@ -3734,16 +3734,16 @@
         <v>39</v>
       </c>
       <c r="B200">
-        <v>15.6225776672363</v>
+        <v>42.162273406982401</v>
       </c>
       <c r="C200">
-        <v>9.8079264480923207</v>
+        <v>31.5719693503776</v>
       </c>
       <c r="D200">
-        <v>15.6197601387773</v>
+        <v>40.858091343601998</v>
       </c>
       <c r="E200">
-        <v>24.0319515767548</v>
+        <v>48.041779621834102</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.2">
@@ -3751,16 +3751,16 @@
         <v>40</v>
       </c>
       <c r="B201">
-        <v>0</v>
+        <v>43.4380073547363</v>
       </c>
       <c r="C201">
-        <v>0</v>
+        <v>38.077642051505698</v>
       </c>
       <c r="D201">
-        <v>0</v>
+        <v>43.8177724410914</v>
       </c>
       <c r="E201">
-        <v>3.4897067199381899</v>
+        <v>50.174184248000699</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.2">
@@ -3768,16 +3768,16 @@
         <v>41</v>
       </c>
       <c r="B202">
-        <v>21.2289123535156</v>
+        <v>8.3194971084594709</v>
       </c>
       <c r="C202">
-        <v>7.2416093696884296</v>
+        <v>2.9479360578090699</v>
       </c>
       <c r="D202">
-        <v>19.013277833429701</v>
+        <v>9.6206805110262206</v>
       </c>
       <c r="E202">
-        <v>32.440461121817101</v>
+        <v>46.163847499037701</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.2">
@@ -3785,16 +3785,16 @@
         <v>42</v>
       </c>
       <c r="B203">
-        <v>24.689191818237301</v>
+        <v>36.149250030517599</v>
       </c>
       <c r="C203">
-        <v>16.143170890142201</v>
+        <v>24.903693968113199</v>
       </c>
       <c r="D203">
-        <v>24.2600783095704</v>
+        <v>34.733349265351698</v>
       </c>
       <c r="E203">
-        <v>33.649660837823497</v>
+        <v>42.602065259629697</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.2">
@@ -3802,16 +3802,16 @@
         <v>43</v>
       </c>
       <c r="B204">
-        <v>27.975894927978501</v>
+        <v>38.1062202453613</v>
       </c>
       <c r="C204">
-        <v>21.505061319834901</v>
+        <v>28.737367872531301</v>
       </c>
       <c r="D204">
-        <v>27.785138934365801</v>
+        <v>36.592323686882203</v>
       </c>
       <c r="E204">
-        <v>34.875309958621301</v>
+        <v>43.5369260813601</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.2">
@@ -3819,16 +3819,16 @@
         <v>44</v>
       </c>
       <c r="B205">
-        <v>35.024604797363303</v>
+        <v>29.6956691741943</v>
       </c>
       <c r="C205">
-        <v>26.344010082760501</v>
+        <v>20.320113625803302</v>
       </c>
       <c r="D205">
-        <v>34.394985444823902</v>
+        <v>28.607515614407401</v>
       </c>
       <c r="E205">
-        <v>43.3112630390251</v>
+        <v>37.117580220502099</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.2">
@@ -3836,16 +3836,16 @@
         <v>45</v>
       </c>
       <c r="B206">
-        <v>24.665889739990199</v>
+        <v>56.061477661132798</v>
       </c>
       <c r="C206">
-        <v>14.350560993858901</v>
+        <v>43.503735882393997</v>
       </c>
       <c r="D206">
-        <v>24.393908561071999</v>
+        <v>52.213019939991398</v>
       </c>
       <c r="E206">
-        <v>27.730538290822299</v>
+        <v>68.230686584971494</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.2">
@@ -3853,16 +3853,16 @@
         <v>46</v>
       </c>
       <c r="B207">
-        <v>20.110898971557599</v>
+        <v>58.513782501220703</v>
       </c>
       <c r="C207">
-        <v>15.718500746116</v>
+        <v>53.392353096071503</v>
       </c>
       <c r="D207">
-        <v>19.730138313711802</v>
+        <v>57.952870995411701</v>
       </c>
       <c r="E207">
-        <v>24.877377736140499</v>
+        <v>64.870630801554796</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.2">
@@ -3870,16 +3870,16 @@
         <v>47</v>
       </c>
       <c r="B208">
-        <v>1.4498751163482699</v>
+        <v>23.101354598998999</v>
       </c>
       <c r="C208">
-        <v>0</v>
+        <v>0.41138884281764898</v>
       </c>
       <c r="D208">
-        <v>1.3998909266810899</v>
+        <v>20.944306854800001</v>
       </c>
       <c r="E208">
-        <v>32.5216523892555</v>
+        <v>34.462986660524699</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.2">
@@ -3887,16 +3887,16 @@
         <v>48</v>
       </c>
       <c r="B209">
-        <v>23.128421783447301</v>
+        <v>12.5999917984009</v>
       </c>
       <c r="C209">
-        <v>15.7442953148439</v>
+        <v>0</v>
       </c>
       <c r="D209">
-        <v>24.453295906754501</v>
+        <v>11.8246318051303</v>
       </c>
       <c r="E209">
-        <v>43.923087526341398</v>
+        <v>25.5289551373506</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.2">
@@ -3904,16 +3904,16 @@
         <v>49</v>
       </c>
       <c r="B210">
-        <v>59.481922149658203</v>
+        <v>0</v>
       </c>
       <c r="C210">
-        <v>42.9456861850406</v>
+        <v>0</v>
       </c>
       <c r="D210">
-        <v>60.5641152383443</v>
+        <v>0</v>
       </c>
       <c r="E210">
-        <v>71.965889650559205</v>
+        <v>4.92287399864541</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.2">
@@ -3921,16 +3921,16 @@
         <v>50</v>
       </c>
       <c r="B211">
-        <v>44.765583038330099</v>
+        <v>21.5766792297363</v>
       </c>
       <c r="C211">
-        <v>38.951718936690099</v>
+        <v>15.8214046492444</v>
       </c>
       <c r="D211">
-        <v>44.542123201644202</v>
+        <v>21.887092121271799</v>
       </c>
       <c r="E211">
-        <v>50.782738253135598</v>
+        <v>27.3571376750936</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.2">
@@ -3938,16 +3938,16 @@
         <v>51</v>
       </c>
       <c r="B212">
-        <v>31.4079685211182</v>
+        <v>45.610118865966797</v>
       </c>
       <c r="C212">
-        <v>27.806988299459199</v>
+        <v>41.5130112330638</v>
       </c>
       <c r="D212">
-        <v>31.169138949463999</v>
+        <v>45.1446474207374</v>
       </c>
       <c r="E212">
-        <v>33.528629462151898</v>
+        <v>49.7629512513154</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.2">
@@ -3955,16 +3955,16 @@
         <v>52</v>
       </c>
       <c r="B213">
-        <v>47.717281341552699</v>
+        <v>32.906566619872997</v>
       </c>
       <c r="C213">
-        <v>40.958445927678497</v>
+        <v>28.378308867331899</v>
       </c>
       <c r="D213">
-        <v>47.099107678542701</v>
+        <v>32.804774661146404</v>
       </c>
       <c r="E213">
-        <v>51.5893668675334</v>
+        <v>38.468942809525402</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.2">
@@ -3972,16 +3972,16 @@
         <v>53</v>
       </c>
       <c r="B214">
-        <v>35.238025665283203</v>
+        <v>40.437858581542997</v>
       </c>
       <c r="C214">
-        <v>31.8633098223481</v>
+        <v>36.581025225810599</v>
       </c>
       <c r="D214">
-        <v>35.010397612783301</v>
+        <v>40.271397438907698</v>
       </c>
       <c r="E214">
-        <v>37.026350970609798</v>
+        <v>44.023757339311402</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.2">
@@ -3989,16 +3989,16 @@
         <v>54</v>
       </c>
       <c r="B215">
-        <v>37.332191467285199</v>
+        <v>36.291301727294901</v>
       </c>
       <c r="C215">
-        <v>33.242521659161198</v>
+        <v>33.083364946528498</v>
       </c>
       <c r="D215">
-        <v>37.345581899636102</v>
+        <v>37.241515609685301</v>
       </c>
       <c r="E215">
-        <v>41.971237422140902</v>
+        <v>42.209953034298699</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.2">
@@ -4006,16 +4006,16 @@
         <v>55</v>
       </c>
       <c r="B216">
-        <v>30.7431240081787</v>
+        <v>39.013877868652301</v>
       </c>
       <c r="C216">
-        <v>27.340302767300599</v>
+        <v>35.248806975129099</v>
       </c>
       <c r="D216">
-        <v>30.790036328409599</v>
+        <v>39.108313687284202</v>
       </c>
       <c r="E216">
-        <v>35.136710163694303</v>
+        <v>42.000143324762703</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.2">
@@ -4023,16 +4023,16 @@
         <v>56</v>
       </c>
       <c r="B217">
-        <v>23.9769992828369</v>
+        <v>0</v>
       </c>
       <c r="C217">
-        <v>16.3838497811123</v>
+        <v>0</v>
       </c>
       <c r="D217">
-        <v>22.944844937182001</v>
+        <v>0</v>
       </c>
       <c r="E217">
-        <v>34.866628462103399</v>
+        <v>1.39291056218413</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.2">
@@ -4040,16 +4040,16 @@
         <v>57</v>
       </c>
       <c r="B218">
-        <v>59.735805511474602</v>
+        <v>16.369256973266602</v>
       </c>
       <c r="C218">
-        <v>52.722059362361698</v>
+        <v>10.4312895917367</v>
       </c>
       <c r="D218">
-        <v>59.213674338428497</v>
+        <v>17.509197710288198</v>
       </c>
       <c r="E218">
-        <v>63.202793583536597</v>
+        <v>25.298932318258</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.2">
@@ -4057,16 +4057,16 @@
         <v>58</v>
       </c>
       <c r="B219">
-        <v>6.7870597839355504</v>
+        <v>47.160324096679702</v>
       </c>
       <c r="C219">
-        <v>1.1520754790787799</v>
+        <v>33.850701635677297</v>
       </c>
       <c r="D219">
-        <v>6.4946760058391098</v>
+        <v>50.0215740150446</v>
       </c>
       <c r="E219">
-        <v>12.9911062947654</v>
+        <v>68.271790897219901</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.2">
@@ -4074,16 +4074,16 @@
         <v>59</v>
       </c>
       <c r="B220">
-        <v>0.32487452030181901</v>
+        <v>0</v>
       </c>
       <c r="C220">
         <v>0</v>
       </c>
       <c r="D220">
-        <v>0.28589754886648699</v>
+        <v>0</v>
       </c>
       <c r="E220">
-        <v>1.2696350479068099</v>
+        <v>4.6324298903804104</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.2">
@@ -4091,16 +4091,16 @@
         <v>60</v>
       </c>
       <c r="B221">
-        <v>1.7829298973083501</v>
+        <v>0</v>
       </c>
       <c r="C221">
         <v>0</v>
       </c>
       <c r="D221">
-        <v>0</v>
+        <v>7.4975242707233001</v>
       </c>
       <c r="E221">
-        <v>2.5802995570884</v>
+        <v>20.8432061362758</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.2">
@@ -4108,16 +4108,16 @@
         <v>61</v>
       </c>
       <c r="B222">
-        <v>0</v>
+        <v>8.7416877746581996</v>
       </c>
       <c r="C222">
-        <v>0</v>
+        <v>6.6510536161793299</v>
       </c>
       <c r="D222">
-        <v>0.24058496774667601</v>
+        <v>8.8623665781524892</v>
       </c>
       <c r="E222">
-        <v>2.3799094976417399</v>
+        <v>18.751092419217802</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.2">
@@ -4147,16 +4147,16 @@
         <v>36</v>
       </c>
       <c r="B226">
-        <v>2.1910643577575701</v>
+        <v>2.26468777656555</v>
       </c>
       <c r="C226">
-        <v>1.46987322127794</v>
+        <v>1.20994507627797</v>
       </c>
       <c r="D226">
-        <v>5.3305393781408501</v>
+        <v>5.0588901968364501</v>
       </c>
       <c r="E226">
-        <v>8.1221584357577896</v>
+        <v>8.0538943556003293</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.2">
@@ -4164,16 +4164,16 @@
         <v>37</v>
       </c>
       <c r="B227">
-        <v>24.486242294311499</v>
+        <v>24.498165130615199</v>
       </c>
       <c r="C227">
-        <v>19.901628597170401</v>
+        <v>20.0557587296083</v>
       </c>
       <c r="D227">
-        <v>22.958860688379598</v>
+        <v>23.176837293341102</v>
       </c>
       <c r="E227">
-        <v>26.8779644895953</v>
+        <v>27.7200812983912</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.2">
@@ -4181,16 +4181,16 @@
         <v>38</v>
       </c>
       <c r="B228">
-        <v>2.51812791824341</v>
+        <v>2.6078088283538801</v>
       </c>
       <c r="C228">
-        <v>1.3624031347506</v>
+        <v>1.3509799120684201</v>
       </c>
       <c r="D228">
-        <v>5.6188243845289403</v>
+        <v>5.3201697924214804</v>
       </c>
       <c r="E228">
-        <v>8.5735742204257903</v>
+        <v>8.4317726744758303</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.2">
@@ -4198,16 +4198,16 @@
         <v>39</v>
       </c>
       <c r="B229">
-        <v>1.64333379268646</v>
+        <v>1.7329246997833301</v>
       </c>
       <c r="C229">
-        <v>1.0294393229276799</v>
+        <v>0.87896743882667405</v>
       </c>
       <c r="D229">
-        <v>3.9602856314346302</v>
+        <v>3.8143227300089602</v>
       </c>
       <c r="E229">
-        <v>7.0622775916316201</v>
+        <v>7.1392056984441998</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.2">
@@ -4215,16 +4215,16 @@
         <v>40</v>
       </c>
       <c r="B230">
-        <v>9.8026046752929705</v>
+        <v>9.8819150924682599</v>
       </c>
       <c r="C230">
-        <v>8.0190934875790401</v>
+        <v>7.9280497496760196</v>
       </c>
       <c r="D230">
-        <v>11.752116301518599</v>
+        <v>11.697973877989901</v>
       </c>
       <c r="E230">
-        <v>15.3242432319462</v>
+        <v>15.208344869849901</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.2">
@@ -4232,16 +4232,16 @@
         <v>41</v>
       </c>
       <c r="B231">
-        <v>10.9411973953247</v>
+        <v>10.973635673522899</v>
       </c>
       <c r="C231">
         <v>0</v>
       </c>
       <c r="D231">
-        <v>5.3936813807360497</v>
+        <v>5.76228437000099</v>
       </c>
       <c r="E231">
-        <v>15.3344373977435</v>
+        <v>15.4976043428669</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.2">
@@ -4249,16 +4249,16 @@
         <v>42</v>
       </c>
       <c r="B232">
-        <v>0</v>
+        <v>8.0624386668205303E-2</v>
       </c>
       <c r="C232">
         <v>0</v>
       </c>
       <c r="D232">
-        <v>1.41996686952176</v>
+        <v>1.4229976285774</v>
       </c>
       <c r="E232">
-        <v>5.3077868955735203</v>
+        <v>5.4838101261602903</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.2">
@@ -4266,16 +4266,16 @@
         <v>43</v>
       </c>
       <c r="B233">
-        <v>0.183493956923485</v>
+        <v>0.256727635860443</v>
       </c>
       <c r="C233">
         <v>0</v>
       </c>
       <c r="D233">
-        <v>1.43101150657108</v>
+        <v>1.35555324957667</v>
       </c>
       <c r="E233">
-        <v>4.3865135279888499</v>
+        <v>4.9574188029660302</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.2">
@@ -4283,16 +4283,16 @@
         <v>44</v>
       </c>
       <c r="B234">
-        <v>0.302094876766205</v>
+        <v>0.350065678358078</v>
       </c>
       <c r="C234">
         <v>0</v>
       </c>
       <c r="D234">
-        <v>0.40712779464749699</v>
+        <v>0.38196935998688297</v>
       </c>
       <c r="E234">
-        <v>3.3050997621347999</v>
+        <v>4.051505064373</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.2">
@@ -4300,16 +4300,16 @@
         <v>45</v>
       </c>
       <c r="B235">
-        <v>1.7186236381530799</v>
+        <v>1.73536205291748</v>
       </c>
       <c r="C235">
         <v>0</v>
       </c>
       <c r="D235">
-        <v>5.9935669648071004</v>
+        <v>5.7198678330092196</v>
       </c>
       <c r="E235">
-        <v>11.151286216633199</v>
+        <v>10.640823447945801</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.2">
@@ -4317,16 +4317,16 @@
         <v>46</v>
       </c>
       <c r="B236">
-        <v>5.4284100532531703</v>
+        <v>5.4471745491027797</v>
       </c>
       <c r="C236">
-        <v>3.27566375847189</v>
+        <v>3.16269209400929</v>
       </c>
       <c r="D236">
-        <v>9.7345476815118008</v>
+        <v>9.4510541535965604</v>
       </c>
       <c r="E236">
-        <v>13.464816207028299</v>
+        <v>13.0579777472147</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.2">
@@ -4334,16 +4334,16 @@
         <v>47</v>
       </c>
       <c r="B237">
-        <v>14.174822807311999</v>
+        <v>14.265911102294901</v>
       </c>
       <c r="C237">
-        <v>2.9465067263084102</v>
+        <v>1.95208555359268</v>
       </c>
       <c r="D237">
-        <v>12.102288286894</v>
+        <v>12.4352772508584</v>
       </c>
       <c r="E237">
-        <v>18.9761837103222</v>
+        <v>19.9923621698319</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.2">
@@ -4351,16 +4351,16 @@
         <v>48</v>
       </c>
       <c r="B238">
-        <v>11.9531354904175</v>
+        <v>12.0029945373535</v>
       </c>
       <c r="C238">
         <v>0</v>
       </c>
       <c r="D238">
-        <v>8.6866971662097701</v>
+        <v>8.7892263989279797</v>
       </c>
       <c r="E238">
-        <v>15.5617279222066</v>
+        <v>15.1419940411997</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.2">
@@ -4368,16 +4368,16 @@
         <v>49</v>
       </c>
       <c r="B239">
-        <v>6.9539051055908203</v>
+        <v>6.9003849029540998</v>
       </c>
       <c r="C239">
         <v>0</v>
       </c>
       <c r="D239">
-        <v>0.81713819611392102</v>
+        <v>1.92949191300203</v>
       </c>
       <c r="E239">
-        <v>10.290586830855499</v>
+        <v>9.6773137541245706</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.2">
@@ -4385,16 +4385,16 @@
         <v>50</v>
       </c>
       <c r="B240">
-        <v>7.4613366127014196</v>
+        <v>7.4322819709777797</v>
       </c>
       <c r="C240">
-        <v>2.2170893409480001</v>
+        <v>2.0755146029155198</v>
       </c>
       <c r="D240">
-        <v>5.5547449778975704</v>
+        <v>5.6264619866313597</v>
       </c>
       <c r="E240">
-        <v>9.4305210489655895</v>
+        <v>9.2083340700471101</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.2">
@@ -4402,16 +4402,16 @@
         <v>51</v>
       </c>
       <c r="B241">
-        <v>4.1147699356079102</v>
+        <v>4.1229505538940403</v>
       </c>
       <c r="C241">
-        <v>2.9757533665118201</v>
+        <v>2.7088958117924502</v>
       </c>
       <c r="D241">
-        <v>6.4933602489371403</v>
+        <v>6.2229981810992703</v>
       </c>
       <c r="E241">
-        <v>8.7268142910058408</v>
+        <v>8.44532016284702</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.2">
@@ -4428,7 +4428,7 @@
         <v>0</v>
       </c>
       <c r="E242">
-        <v>1.8057906447577301</v>
+        <v>1.27628186294602</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.2">
@@ -4436,16 +4436,16 @@
         <v>53</v>
       </c>
       <c r="B243">
-        <v>5.3288946151733398</v>
+        <v>5.3225793838501003</v>
       </c>
       <c r="C243">
-        <v>4.3996563734535403</v>
+        <v>4.2216666722738303</v>
       </c>
       <c r="D243">
-        <v>6.6709421630071999</v>
+        <v>6.4341791082163198</v>
       </c>
       <c r="E243">
-        <v>8.4229085823339496</v>
+        <v>8.1261942161237197</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.2">
@@ -4453,16 +4453,16 @@
         <v>54</v>
       </c>
       <c r="B244">
-        <v>16.889762878418001</v>
+        <v>16.8426322937012</v>
       </c>
       <c r="C244">
-        <v>12.9075551847776</v>
+        <v>12.929179008045899</v>
       </c>
       <c r="D244">
-        <v>16.001308272043499</v>
+        <v>15.9703131421868</v>
       </c>
       <c r="E244">
-        <v>18.5066713179997</v>
+        <v>18.385162353691101</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.2">
@@ -4470,16 +4470,16 @@
         <v>55</v>
       </c>
       <c r="B245">
-        <v>13.3336801528931</v>
+        <v>13.298243522644</v>
       </c>
       <c r="C245">
-        <v>10.9968637437266</v>
+        <v>10.181134382833299</v>
       </c>
       <c r="D245">
-        <v>13.291533638767801</v>
+        <v>13.2879397965766</v>
       </c>
       <c r="E245">
-        <v>15.216919504651599</v>
+        <v>15.3015173427658</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.2">
@@ -4487,16 +4487,16 @@
         <v>56</v>
       </c>
       <c r="B246">
-        <v>34.082267761230497</v>
+        <v>33.9259033203125</v>
       </c>
       <c r="C246">
-        <v>14.457766826024899</v>
+        <v>14.7935570772412</v>
       </c>
       <c r="D246">
-        <v>25.399771291842601</v>
+        <v>26.719150064729</v>
       </c>
       <c r="E246">
-        <v>49.135579795094102</v>
+        <v>49.866543881557902</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.2">
@@ -4504,16 +4504,16 @@
         <v>57</v>
       </c>
       <c r="B247">
-        <v>6.7317361831665004</v>
+        <v>6.6735706329345703</v>
       </c>
       <c r="C247">
-        <v>1.6367490443428501</v>
+        <v>1.9281339327782501</v>
       </c>
       <c r="D247">
-        <v>4.1079447867565504</v>
+        <v>4.3915959206499497</v>
       </c>
       <c r="E247">
-        <v>7.8441418673368002</v>
+        <v>7.8963316840523703</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.2">
@@ -4521,16 +4521,16 @@
         <v>58</v>
       </c>
       <c r="B248">
-        <v>14.1074895858765</v>
+        <v>14.0718631744385</v>
       </c>
       <c r="C248">
-        <v>6.2567204342083098</v>
+        <v>6.8838649363507498</v>
       </c>
       <c r="D248">
-        <v>14.9297900373203</v>
+        <v>14.5950906543821</v>
       </c>
       <c r="E248">
-        <v>26.470924526797699</v>
+        <v>24.985751906782099</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.2">
@@ -4538,16 +4538,16 @@
         <v>59</v>
       </c>
       <c r="B249">
-        <v>53.0390434265137</v>
+        <v>53.074333190917997</v>
       </c>
       <c r="C249">
-        <v>31.4171460641419</v>
+        <v>32.576627397523097</v>
       </c>
       <c r="D249">
-        <v>45.115575811814601</v>
+        <v>46.9120689689831</v>
       </c>
       <c r="E249">
-        <v>57.210974035725201</v>
+        <v>58.449235986027396</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.2">
@@ -4564,7 +4564,7 @@
         <v>0</v>
       </c>
       <c r="E250">
-        <v>3.16343805406057</v>
+        <v>4.0551255523154897</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.2">
@@ -4572,16 +4572,16 @@
         <v>61</v>
       </c>
       <c r="B251">
-        <v>87.859771728515597</v>
+        <v>87.883804321289105</v>
       </c>
       <c r="C251">
-        <v>65.439340922741707</v>
+        <v>67.368868536115897</v>
       </c>
       <c r="D251">
-        <v>80.357294846981304</v>
+        <v>81.302415543828701</v>
       </c>
       <c r="E251">
-        <v>88.518476672364898</v>
+        <v>89.349357528598404</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.2">
@@ -4611,16 +4611,16 @@
         <v>36</v>
       </c>
       <c r="B255">
-        <v>47.626781463622997</v>
+        <v>14.839266777038601</v>
       </c>
       <c r="C255">
-        <v>37.839328719858599</v>
+        <v>9.4648488978269096</v>
       </c>
       <c r="D255">
-        <v>46.376341448226398</v>
+        <v>14.931919196284801</v>
       </c>
       <c r="E255">
-        <v>53.101767174494299</v>
+        <v>20.412331864621201</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.2">
@@ -4628,16 +4628,16 @@
         <v>37</v>
       </c>
       <c r="B256">
-        <v>35.324127197265597</v>
+        <v>3.4414489269256601</v>
       </c>
       <c r="C256">
-        <v>29.367157982230498</v>
+        <v>0</v>
       </c>
       <c r="D256">
-        <v>36.808571735189602</v>
+        <v>3.4460954599807399</v>
       </c>
       <c r="E256">
-        <v>44.7226961211963</v>
+        <v>6.1821751659100599</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.2">
@@ -4645,16 +4645,16 @@
         <v>38</v>
       </c>
       <c r="B257">
-        <v>48.023754119872997</v>
+        <v>12.270834922790501</v>
       </c>
       <c r="C257">
-        <v>40.611234741603703</v>
+        <v>9.0135326270206608</v>
       </c>
       <c r="D257">
-        <v>47.323777418322202</v>
+        <v>12.374673649771401</v>
       </c>
       <c r="E257">
-        <v>52.094762654234799</v>
+        <v>16.948578992146299</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.2">
@@ -4662,16 +4662,16 @@
         <v>39</v>
       </c>
       <c r="B258">
-        <v>42.265460968017599</v>
+        <v>15.6521644592285</v>
       </c>
       <c r="C258">
-        <v>32.2287318895456</v>
+        <v>9.8388521632185704</v>
       </c>
       <c r="D258">
-        <v>41.222584887048697</v>
+        <v>15.529256867566099</v>
       </c>
       <c r="E258">
-        <v>47.817653016512203</v>
+        <v>24.346471985292801</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.2">
@@ -4679,16 +4679,16 @@
         <v>40</v>
       </c>
       <c r="B259">
-        <v>43.551502227783203</v>
+        <v>0</v>
       </c>
       <c r="C259">
-        <v>38.400880159315399</v>
+        <v>0</v>
       </c>
       <c r="D259">
-        <v>43.836620210597502</v>
+        <v>0</v>
       </c>
       <c r="E259">
-        <v>50.150823164446699</v>
+        <v>4.1705792400175499</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.2">
@@ -4696,16 +4696,16 @@
         <v>41</v>
       </c>
       <c r="B260">
-        <v>8.2788763046264595</v>
+        <v>21.293577194213899</v>
       </c>
       <c r="C260">
-        <v>3.0379135248911902</v>
+        <v>7.9550447375377997</v>
       </c>
       <c r="D260">
-        <v>9.1949513045186908</v>
+        <v>18.540161491480301</v>
       </c>
       <c r="E260">
-        <v>46.916994348303497</v>
+        <v>35.017790225042098</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.2">
@@ -4713,16 +4713,16 @@
         <v>42</v>
       </c>
       <c r="B261">
-        <v>36.226005554199197</v>
+        <v>24.741432189941399</v>
       </c>
       <c r="C261">
-        <v>26.058525615099899</v>
+        <v>16.430682286633601</v>
       </c>
       <c r="D261">
-        <v>34.5799186639493</v>
+        <v>24.161626654141301</v>
       </c>
       <c r="E261">
-        <v>42.376289373574302</v>
+        <v>34.608016800620099</v>
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.2">
@@ -4730,16 +4730,16 @@
         <v>43</v>
       </c>
       <c r="B262">
-        <v>38.194236755371101</v>
+        <v>28.034254074096701</v>
       </c>
       <c r="C262">
-        <v>29.037270742508099</v>
+        <v>21.9247065315285</v>
       </c>
       <c r="D262">
-        <v>36.550127110376899</v>
+        <v>27.821312875619601</v>
       </c>
       <c r="E262">
-        <v>43.286174479860001</v>
+        <v>34.7996680570389</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.2">
@@ -4747,16 +4747,16 @@
         <v>44</v>
       </c>
       <c r="B263">
-        <v>29.765403747558601</v>
+        <v>35.1049995422363</v>
       </c>
       <c r="C263">
-        <v>21.174921511954299</v>
+        <v>26.895345816787</v>
       </c>
       <c r="D263">
-        <v>28.9818645927955</v>
+        <v>34.440093681635403</v>
       </c>
       <c r="E263">
-        <v>37.214706355887103</v>
+        <v>43.984109093843102</v>
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.2">
@@ -4764,16 +4764,16 @@
         <v>45</v>
       </c>
       <c r="B264">
-        <v>56.321361541747997</v>
+        <v>24.762153625488299</v>
       </c>
       <c r="C264">
-        <v>44.334391256579401</v>
+        <v>14.9494388132232</v>
       </c>
       <c r="D264">
-        <v>54.094275774526103</v>
+        <v>24.7989605790128</v>
       </c>
       <c r="E264">
-        <v>69.713446241172207</v>
+        <v>27.671424642353301</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.2">
@@ -4781,16 +4781,16 @@
         <v>46</v>
       </c>
       <c r="B265">
-        <v>58.677684783935497</v>
+        <v>20.136920928955099</v>
       </c>
       <c r="C265">
-        <v>53.902916302076498</v>
+        <v>15.844554796791501</v>
       </c>
       <c r="D265">
-        <v>57.975783991008797</v>
+        <v>19.8207046865266</v>
       </c>
       <c r="E265">
-        <v>65.337247138925093</v>
+        <v>25.1792925357346</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.2">
@@ -4798,16 +4798,16 @@
         <v>47</v>
       </c>
       <c r="B266">
-        <v>23.128456115722699</v>
+        <v>1.44920122623444</v>
       </c>
       <c r="C266">
         <v>0</v>
       </c>
       <c r="D266">
-        <v>21.2957472541285</v>
+        <v>1.78426731990236</v>
       </c>
       <c r="E266">
-        <v>34.749188626104697</v>
+        <v>33.046057570747898</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.2">
@@ -4815,16 +4815,16 @@
         <v>48</v>
       </c>
       <c r="B267">
-        <v>12.610050201416</v>
+        <v>23.175512313842798</v>
       </c>
       <c r="C267">
-        <v>0</v>
+        <v>16.347508136556801</v>
       </c>
       <c r="D267">
-        <v>11.0335801480201</v>
+        <v>24.5921729263877</v>
       </c>
       <c r="E267">
-        <v>27.738419575879401</v>
+        <v>44.480727706856101</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.2">
@@ -4832,16 +4832,16 @@
         <v>49</v>
       </c>
       <c r="B268">
-        <v>0</v>
+        <v>59.655845642089801</v>
       </c>
       <c r="C268">
-        <v>0</v>
+        <v>42.086663081910203</v>
       </c>
       <c r="D268">
-        <v>0</v>
+        <v>60.655747620957797</v>
       </c>
       <c r="E268">
-        <v>4.3712679949518103</v>
+        <v>71.822730556838906</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.2">
@@ -4849,16 +4849,16 @@
         <v>50</v>
       </c>
       <c r="B269">
-        <v>21.6320705413818</v>
+        <v>44.872936248779297</v>
       </c>
       <c r="C269">
-        <v>15.367846677897299</v>
+        <v>39.068433206705599</v>
       </c>
       <c r="D269">
-        <v>22.004208183378601</v>
+        <v>44.617401652388203</v>
       </c>
       <c r="E269">
-        <v>27.782668277591299</v>
+        <v>50.479665869278698</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.2">
@@ -4866,16 +4866,16 @@
         <v>51</v>
       </c>
       <c r="B270">
-        <v>45.734855651855497</v>
+        <v>31.463912963867202</v>
       </c>
       <c r="C270">
-        <v>42.169424301006501</v>
+        <v>27.722962679174</v>
       </c>
       <c r="D270">
-        <v>45.417662315687103</v>
+        <v>31.3543595615788</v>
       </c>
       <c r="E270">
-        <v>49.795280208457001</v>
+        <v>33.548640087925797</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.2">
@@ -4883,16 +4883,16 @@
         <v>52</v>
       </c>
       <c r="B271">
-        <v>32.999385833740199</v>
+        <v>47.820888519287102</v>
       </c>
       <c r="C271">
-        <v>28.704103473096598</v>
+        <v>41.243070013707097</v>
       </c>
       <c r="D271">
-        <v>33.366302429351897</v>
+        <v>47.272975580069698</v>
       </c>
       <c r="E271">
-        <v>38.255763876615703</v>
+        <v>51.535461088511703</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.2">
@@ -4900,16 +4900,16 @@
         <v>53</v>
       </c>
       <c r="B272">
-        <v>40.5486030578613</v>
+        <v>35.308319091796903</v>
       </c>
       <c r="C272">
-        <v>37.303213100831897</v>
+        <v>32.041565069831599</v>
       </c>
       <c r="D272">
-        <v>40.628056635824201</v>
+        <v>35.115358041534201</v>
       </c>
       <c r="E272">
-        <v>44.446001894262103</v>
+        <v>37.257293102150101</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.2">
@@ -4917,16 +4917,16 @@
         <v>54</v>
       </c>
       <c r="B273">
-        <v>36.388057708740199</v>
+        <v>37.412242889404297</v>
       </c>
       <c r="C273">
-        <v>32.898435337664601</v>
+        <v>33.030422472645398</v>
       </c>
       <c r="D273">
-        <v>37.188936315661103</v>
+        <v>37.418539776420999</v>
       </c>
       <c r="E273">
-        <v>42.205768920790398</v>
+        <v>42.2037681037799</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.2">
@@ -4934,16 +4934,16 @@
         <v>55</v>
       </c>
       <c r="B274">
-        <v>39.1140747070313</v>
+        <v>30.8067417144775</v>
       </c>
       <c r="C274">
-        <v>35.110197563988599</v>
+        <v>27.101201282839799</v>
       </c>
       <c r="D274">
-        <v>38.9642317536997</v>
+        <v>30.885777279356901</v>
       </c>
       <c r="E274">
-        <v>42.046943875295099</v>
+        <v>35.582644978116001</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.2">
@@ -4951,16 +4951,16 @@
         <v>56</v>
       </c>
       <c r="B275">
-        <v>0</v>
+        <v>24.049392700195298</v>
       </c>
       <c r="C275">
-        <v>0</v>
+        <v>15.523135751597399</v>
       </c>
       <c r="D275">
-        <v>0</v>
+        <v>23.009797120919899</v>
       </c>
       <c r="E275">
-        <v>0</v>
+        <v>35.390364104905402</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.2">
@@ -4968,16 +4968,16 @@
         <v>57</v>
       </c>
       <c r="B276">
-        <v>16.434352874755898</v>
+        <v>59.905647277832003</v>
       </c>
       <c r="C276">
-        <v>10.788560244723501</v>
+        <v>53.3076035368859</v>
       </c>
       <c r="D276">
-        <v>17.437336388122802</v>
+        <v>59.4917844046848</v>
       </c>
       <c r="E276">
-        <v>24.913869611733102</v>
+        <v>63.779744561605099</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.2">
@@ -4985,16 +4985,16 @@
         <v>58</v>
       </c>
       <c r="B277">
-        <v>47.159008026122997</v>
+        <v>6.7769966125488299</v>
       </c>
       <c r="C277">
-        <v>34.626837193113097</v>
+        <v>1.2667655119779</v>
       </c>
       <c r="D277">
-        <v>49.404595694967199</v>
+        <v>6.2868281519438396</v>
       </c>
       <c r="E277">
-        <v>67.900610519371895</v>
+        <v>12.597623073803</v>
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.2">
@@ -5002,16 +5002,16 @@
         <v>59</v>
       </c>
       <c r="B278">
-        <v>0</v>
+        <v>0.32407692074775701</v>
       </c>
       <c r="C278">
         <v>0</v>
       </c>
       <c r="D278">
-        <v>0</v>
+        <v>0.30543650092237301</v>
       </c>
       <c r="E278">
-        <v>3.44202910550506</v>
+        <v>1.33569903161651</v>
       </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.2">
@@ -5019,16 +5019,16 @@
         <v>60</v>
       </c>
       <c r="B279">
-        <v>0</v>
+        <v>1.8181246519088701</v>
       </c>
       <c r="C279">
         <v>0</v>
       </c>
       <c r="D279">
-        <v>7.8438076512546298</v>
+        <v>0</v>
       </c>
       <c r="E279">
-        <v>21.301508312669501</v>
+        <v>3.2490033387775599</v>
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.2">
@@ -5036,16 +5036,16 @@
         <v>61</v>
       </c>
       <c r="B280">
-        <v>8.7818155288696307</v>
+        <v>0</v>
       </c>
       <c r="C280">
-        <v>6.1701100920344496</v>
+        <v>0</v>
       </c>
       <c r="D280">
-        <v>8.9345402750889207</v>
+        <v>0.55630032270354002</v>
       </c>
       <c r="E280">
-        <v>16.554758045799801</v>
+        <v>2.69221783631082</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.2">
@@ -5075,16 +5075,16 @@
         <v>36</v>
       </c>
       <c r="B284">
-        <v>11.9854431152344</v>
+        <v>12.047830581665</v>
       </c>
       <c r="C284">
-        <v>6.9162266215622603</v>
+        <v>7.6335421771234904</v>
       </c>
       <c r="D284">
-        <v>10.462169655659199</v>
+        <v>10.6841081799445</v>
       </c>
       <c r="E284">
-        <v>14.5767387884211</v>
+        <v>15.2117423106488</v>
       </c>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.2">
@@ -5092,16 +5092,16 @@
         <v>37</v>
       </c>
       <c r="B285">
-        <v>17.633205413818398</v>
+        <v>17.704687118530298</v>
       </c>
       <c r="C285">
-        <v>9.9302415751791298</v>
+        <v>8.7989703288713699</v>
       </c>
       <c r="D285">
-        <v>17.5518058572078</v>
+        <v>17.176365370705501</v>
       </c>
       <c r="E285">
-        <v>24.886194356638001</v>
+        <v>23.987971412528701</v>
       </c>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.2">
@@ -5109,16 +5109,16 @@
         <v>38</v>
       </c>
       <c r="B286">
-        <v>9.6360912322997994</v>
+        <v>9.6801567077636701</v>
       </c>
       <c r="C286">
-        <v>4.2327881150877502</v>
+        <v>4.3652270304282599</v>
       </c>
       <c r="D286">
-        <v>7.8243608277804597</v>
+        <v>8.1046418815147501</v>
       </c>
       <c r="E286">
-        <v>11.9094645934418</v>
+        <v>11.837263157200599</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.2">
@@ -5126,16 +5126,16 @@
         <v>39</v>
       </c>
       <c r="B287">
-        <v>7.7367024421691903</v>
+        <v>7.7651057243347203</v>
       </c>
       <c r="C287">
-        <v>3.7328859401135501</v>
+        <v>3.81162723927403</v>
       </c>
       <c r="D287">
-        <v>7.1381124053918903</v>
+        <v>7.3113001448857</v>
       </c>
       <c r="E287">
-        <v>12.4004886727319</v>
+        <v>12.6395682096367</v>
       </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.2">
@@ -5143,16 +5143,16 @@
         <v>40</v>
       </c>
       <c r="B288">
-        <v>18.644126892089801</v>
+        <v>18.7100734710693</v>
       </c>
       <c r="C288">
-        <v>10.2711257896991</v>
+        <v>10.149213256431899</v>
       </c>
       <c r="D288">
-        <v>17.511947738499501</v>
+        <v>17.4990205780956</v>
       </c>
       <c r="E288">
-        <v>23.398055760344199</v>
+        <v>23.668230823702999</v>
       </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.2">
@@ -5160,16 +5160,16 @@
         <v>41</v>
       </c>
       <c r="B289">
-        <v>4.120361328125</v>
+        <v>4.04728078842163</v>
       </c>
       <c r="C289">
         <v>0</v>
       </c>
       <c r="D289">
-        <v>8.6043853718301193</v>
+        <v>7.6399955053455804</v>
       </c>
       <c r="E289">
-        <v>22.261958040988201</v>
+        <v>21.093614832195499</v>
       </c>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.2">
@@ -5186,7 +5186,7 @@
         <v>0</v>
       </c>
       <c r="E290">
-        <v>4.0956792407315703</v>
+        <v>4.60770134740652</v>
       </c>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.2">
@@ -5203,7 +5203,7 @@
         <v>0</v>
       </c>
       <c r="E291">
-        <v>3.7646959118740799</v>
+        <v>3.8122980283449199</v>
       </c>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.2">
@@ -5211,16 +5211,16 @@
         <v>44</v>
       </c>
       <c r="B292">
-        <v>2.1229403093457201E-2</v>
+        <v>3.0141597613692301E-2</v>
       </c>
       <c r="C292">
         <v>0</v>
       </c>
       <c r="D292">
-        <v>1.63298007089582</v>
+        <v>1.6829901621061001</v>
       </c>
       <c r="E292">
-        <v>7.1818767736476303</v>
+        <v>7.5259037401323399</v>
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.2">
@@ -5228,16 +5228,16 @@
         <v>45</v>
       </c>
       <c r="B293">
-        <v>15.4918880462646</v>
+        <v>15.693783760070801</v>
       </c>
       <c r="C293">
         <v>0</v>
       </c>
       <c r="D293">
-        <v>8.7084744172668902</v>
+        <v>9.9198897841112501</v>
       </c>
       <c r="E293">
-        <v>21.022391949361602</v>
+        <v>22.650665308506799</v>
       </c>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.2">
@@ -5245,16 +5245,16 @@
         <v>46</v>
       </c>
       <c r="B294">
-        <v>15.7830047607422</v>
+        <v>15.9021196365356</v>
       </c>
       <c r="C294">
         <v>0</v>
       </c>
       <c r="D294">
-        <v>12.2918632755686</v>
+        <v>13.126893083980899</v>
       </c>
       <c r="E294">
-        <v>17.887990368388301</v>
+        <v>18.4867561050776</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.2">
@@ -5262,16 +5262,16 @@
         <v>47</v>
       </c>
       <c r="B295">
-        <v>9.1248521804809606</v>
+        <v>9.1358356475830096</v>
       </c>
       <c r="C295">
-        <v>0.43089244213294697</v>
+        <v>0.41168630168299802</v>
       </c>
       <c r="D295">
-        <v>12.7043160204326</v>
+        <v>12.8536683882533</v>
       </c>
       <c r="E295">
-        <v>30.441738563043799</v>
+        <v>29.9070203288275</v>
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.2">
@@ -5288,7 +5288,7 @@
         <v>0</v>
       </c>
       <c r="E296">
-        <v>21.321606386556901</v>
+        <v>23.573859704469399</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.2">
@@ -5302,10 +5302,10 @@
         <v>0</v>
       </c>
       <c r="D297">
-        <v>4.5302252312473303</v>
+        <v>4.2148042380513502</v>
       </c>
       <c r="E297">
-        <v>21.156904822783499</v>
+        <v>18.021322072161901</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.2">
@@ -5313,16 +5313,16 @@
         <v>50</v>
       </c>
       <c r="B298">
-        <v>7.3490552902221697</v>
+        <v>7.4056158065795898</v>
       </c>
       <c r="C298">
-        <v>5.6007707942632399</v>
+        <v>5.6708248604523801</v>
       </c>
       <c r="D298">
-        <v>9.9138222733508208</v>
+        <v>9.8111545448503197</v>
       </c>
       <c r="E298">
-        <v>17.291497384778399</v>
+        <v>16.7170057026192</v>
       </c>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.2">
@@ -5330,16 +5330,16 @@
         <v>51</v>
       </c>
       <c r="B299">
-        <v>12.1954555511475</v>
+        <v>12.2877292633057</v>
       </c>
       <c r="C299">
-        <v>4.0135857420357901</v>
+        <v>4.3014599547317696</v>
       </c>
       <c r="D299">
-        <v>10.853050027895099</v>
+        <v>11.4982877688043</v>
       </c>
       <c r="E299">
-        <v>15.112109854881099</v>
+        <v>15.6041745813685</v>
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.2">
@@ -5347,16 +5347,16 @@
         <v>52</v>
       </c>
       <c r="B300">
-        <v>2.0368185043335001</v>
+        <v>2.0868847370147701</v>
       </c>
       <c r="C300">
         <v>0</v>
       </c>
       <c r="D300">
-        <v>2.26615246104158</v>
+        <v>2.5244214965457701</v>
       </c>
       <c r="E300">
-        <v>7.3263918905028396</v>
+        <v>7.6361776612967303</v>
       </c>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.2">
@@ -5364,16 +5364,16 @@
         <v>53</v>
       </c>
       <c r="B301">
-        <v>10.730725288391101</v>
+        <v>10.818879127502401</v>
       </c>
       <c r="C301">
-        <v>4.9421963505381603</v>
+        <v>4.9476887961125504</v>
       </c>
       <c r="D301">
-        <v>10.154008054457</v>
+        <v>10.560178874781201</v>
       </c>
       <c r="E301">
-        <v>14.302178069382499</v>
+        <v>14.466505657401999</v>
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.2">
@@ -5381,16 +5381,16 @@
         <v>54</v>
       </c>
       <c r="B302">
-        <v>9.3899879455566406</v>
+        <v>9.4538221359252894</v>
       </c>
       <c r="C302">
-        <v>1.1879486866048701</v>
+        <v>1.3633075756444799</v>
       </c>
       <c r="D302">
-        <v>9.4590530417312095</v>
+        <v>9.4282842834072902</v>
       </c>
       <c r="E302">
-        <v>13.260071616405201</v>
+        <v>13.175565696661501</v>
       </c>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.2">
@@ -5398,16 +5398,16 @@
         <v>55</v>
       </c>
       <c r="B303">
-        <v>14.2855882644653</v>
+        <v>14.391993522644</v>
       </c>
       <c r="C303">
-        <v>8.5259419445820193</v>
+        <v>8.6209399167691299</v>
       </c>
       <c r="D303">
-        <v>13.860657924803901</v>
+        <v>14.017106200482401</v>
       </c>
       <c r="E303">
-        <v>17.186702373337098</v>
+        <v>17.045609816041399</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.2">
@@ -5415,16 +5415,16 @@
         <v>56</v>
       </c>
       <c r="B304">
-        <v>41.714073181152301</v>
+        <v>41.947227478027301</v>
       </c>
       <c r="C304">
-        <v>17.537124011998198</v>
+        <v>19.446537943715398</v>
       </c>
       <c r="D304">
-        <v>48.685173933578902</v>
+        <v>46.363752296288901</v>
       </c>
       <c r="E304">
-        <v>61.447508774933098</v>
+        <v>61.438514936965603</v>
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.2">
@@ -5432,16 +5432,16 @@
         <v>57</v>
       </c>
       <c r="B305">
-        <v>0.23314584791660301</v>
+        <v>0.27130067348480202</v>
       </c>
       <c r="C305">
         <v>0</v>
       </c>
       <c r="D305">
-        <v>2.8045723729813199</v>
+        <v>2.8746745821121999</v>
       </c>
       <c r="E305">
-        <v>8.8038147252714207</v>
+        <v>9.4765240899179393</v>
       </c>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.2">
@@ -5449,16 +5449,16 @@
         <v>58</v>
       </c>
       <c r="B306">
-        <v>29.070959091186499</v>
+        <v>29.125576019287099</v>
       </c>
       <c r="C306">
-        <v>5.9382028855719797</v>
+        <v>4.9793409429927697</v>
       </c>
       <c r="D306">
-        <v>24.072623951375199</v>
+        <v>24.6769775713441</v>
       </c>
       <c r="E306">
-        <v>35.973068853061598</v>
+        <v>36.131449786286403</v>
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.2">
@@ -5466,16 +5466,16 @@
         <v>59</v>
       </c>
       <c r="B307">
-        <v>3.2378766536712602</v>
+        <v>3.19921827316284</v>
       </c>
       <c r="C307">
         <v>0</v>
       </c>
       <c r="D307">
-        <v>5.9168631133691196</v>
+        <v>5.2033904424194297</v>
       </c>
       <c r="E307">
-        <v>33.405348058872001</v>
+        <v>33.553595987460703</v>
       </c>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.2">
@@ -5483,16 +5483,16 @@
         <v>60</v>
       </c>
       <c r="B308">
-        <v>78.321578979492202</v>
+        <v>78.507965087890597</v>
       </c>
       <c r="C308">
-        <v>62.270379543397098</v>
+        <v>60.054643434107597</v>
       </c>
       <c r="D308">
-        <v>78.481567686846603</v>
+        <v>80.151843407555006</v>
       </c>
       <c r="E308">
-        <v>90.290550905992006</v>
+        <v>90.774039865449595</v>
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.2">
@@ -5509,7 +5509,7 @@
         <v>0</v>
       </c>
       <c r="E309">
-        <v>18.8997493190003</v>
+        <v>18.410734650678901</v>
       </c>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.2">
@@ -5539,16 +5539,16 @@
         <v>36</v>
       </c>
       <c r="B313">
-        <v>19.207065421353501</v>
+        <v>19.166180077639599</v>
       </c>
       <c r="C313">
-        <v>23.913270950317401</v>
+        <v>24.331569671630898</v>
       </c>
       <c r="D313">
-        <v>19.037569046020501</v>
+        <v>19.110488891601602</v>
       </c>
       <c r="E313">
-        <v>15.2115888595581</v>
+        <v>15.415662765502899</v>
       </c>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.2">
@@ -5556,16 +5556,16 @@
         <v>37</v>
       </c>
       <c r="B314">
-        <v>6.0018542042814902</v>
+        <v>5.9886915846367499</v>
       </c>
       <c r="C314">
-        <v>6.0498089790344203</v>
+        <v>5.8685641288757298</v>
       </c>
       <c r="D314">
-        <v>6.1246991157531703</v>
+        <v>6.0592780113220197</v>
       </c>
       <c r="E314">
-        <v>5.5341753959655797</v>
+        <v>5.5058608055114702</v>
       </c>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.2">
@@ -5573,16 +5573,16 @@
         <v>38</v>
       </c>
       <c r="B315">
-        <v>3.4287300200291102</v>
+        <v>3.4225438978265301</v>
       </c>
       <c r="C315">
-        <v>4.2034535408020002</v>
+        <v>4.2609796524047896</v>
       </c>
       <c r="D315">
-        <v>3.34398245811462</v>
+        <v>3.3914318084716801</v>
       </c>
       <c r="E315">
-        <v>2.7758941650390598</v>
+        <v>2.8691968917846702</v>
       </c>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.2">
@@ -5590,16 +5590,16 @@
         <v>39</v>
       </c>
       <c r="B316">
-        <v>5.8724056177119799</v>
+        <v>5.85973902656721</v>
       </c>
       <c r="C316">
-        <v>7.2006072998046902</v>
+        <v>7.1739845275878897</v>
       </c>
       <c r="D316">
-        <v>5.58241844177246</v>
+        <v>5.6719331741332999</v>
       </c>
       <c r="E316">
-        <v>4.5407085418701199</v>
+        <v>4.6398735046386701</v>
       </c>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.2">
@@ -5607,16 +5607,16 @@
         <v>40</v>
       </c>
       <c r="B317">
-        <v>13.682254727852801</v>
+        <v>13.6563142439992</v>
       </c>
       <c r="C317">
-        <v>12.671582221984901</v>
+        <v>11.9412031173706</v>
       </c>
       <c r="D317">
-        <v>13.2825813293457</v>
+        <v>13.3486652374268</v>
       </c>
       <c r="E317">
-        <v>11.7031955718994</v>
+        <v>11.8296499252319</v>
       </c>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.2">
@@ -5624,16 +5624,16 @@
         <v>41</v>
       </c>
       <c r="B318">
-        <v>1.7502645555716201</v>
+        <v>1.74583189197779</v>
       </c>
       <c r="C318">
-        <v>1.4588031768798799</v>
+        <v>1.4492495059967001</v>
       </c>
       <c r="D318">
-        <v>1.54083144664764</v>
+        <v>1.54506659507751</v>
       </c>
       <c r="E318">
-        <v>1.5087265968322801</v>
+        <v>1.5257163047790501</v>
       </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.2">
@@ -5641,16 +5641,16 @@
         <v>42</v>
       </c>
       <c r="B319">
-        <v>2.9537078800566801</v>
+        <v>2.9465125298604602</v>
       </c>
       <c r="C319">
-        <v>3.21346116065979</v>
+        <v>3.2067015171050999</v>
       </c>
       <c r="D319">
-        <v>2.8189315795898402</v>
+        <v>2.8534853458404501</v>
       </c>
       <c r="E319">
-        <v>2.5649757385253902</v>
+        <v>2.55486965179443</v>
       </c>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.2">
@@ -5658,16 +5658,16 @@
         <v>43</v>
       </c>
       <c r="B320">
-        <v>1.1850084227125099</v>
+        <v>1.1823527727140799</v>
       </c>
       <c r="C320">
-        <v>1.3214017152786299</v>
+        <v>1.3367748260498</v>
       </c>
       <c r="D320">
-        <v>1.1306337118148799</v>
+        <v>1.13405621051788</v>
       </c>
       <c r="E320">
-        <v>0.99907302856445301</v>
+        <v>0.98927766084670998</v>
       </c>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.2">
@@ -5675,16 +5675,16 @@
         <v>44</v>
       </c>
       <c r="B321">
-        <v>3.35377759045388</v>
+        <v>3.3434792956194599</v>
       </c>
       <c r="C321">
-        <v>3.4296138286590598</v>
+        <v>3.4881820678710902</v>
       </c>
       <c r="D321">
-        <v>3.1273212432861301</v>
+        <v>3.1343331336975102</v>
       </c>
       <c r="E321">
-        <v>2.8357450962066699</v>
+        <v>2.8783524036407502</v>
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.2">
@@ -5692,16 +5692,16 @@
         <v>45</v>
       </c>
       <c r="B322">
-        <v>0.414793375365546</v>
+        <v>0.40194734257163101</v>
       </c>
       <c r="C322">
         <v>0</v>
       </c>
       <c r="D322">
-        <v>0.87363421916961703</v>
+        <v>0.88813197612762496</v>
       </c>
       <c r="E322">
-        <v>2.7069344520568799</v>
+        <v>2.6392655372619598</v>
       </c>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.2">
@@ -5718,7 +5718,7 @@
         <v>0</v>
       </c>
       <c r="E323">
-        <v>1.5245891809463501</v>
+        <v>1.50836765766144</v>
       </c>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.2">
@@ -5726,16 +5726,16 @@
         <v>47</v>
       </c>
       <c r="B324">
-        <v>3.1874592003392799</v>
+        <v>3.1784463213660299</v>
       </c>
       <c r="C324">
-        <v>3.3211743831634499</v>
+        <v>2.9920411109924299</v>
       </c>
       <c r="D324">
-        <v>3.0334157943725599</v>
+        <v>3.0398697853088401</v>
       </c>
       <c r="E324">
-        <v>2.7348880767822301</v>
+        <v>2.8197169303893999</v>
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.2">
@@ -5743,16 +5743,16 @@
         <v>48</v>
       </c>
       <c r="B325">
-        <v>4.3715782198961</v>
+        <v>4.35668970727101</v>
       </c>
       <c r="C325">
-        <v>3.9047396183013898</v>
+        <v>3.9024698734283398</v>
       </c>
       <c r="D325">
-        <v>4.1030750274658203</v>
+        <v>4.0781211853027299</v>
       </c>
       <c r="E325">
-        <v>4.1242046356201199</v>
+        <v>4.08154249191284</v>
       </c>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.2">
@@ -5760,16 +5760,16 @@
         <v>49</v>
       </c>
       <c r="B326">
-        <v>3.53707549535899</v>
+        <v>3.5184569859509098</v>
       </c>
       <c r="C326">
-        <v>2.36439776420593</v>
+        <v>2.6024019718170202</v>
       </c>
       <c r="D326">
-        <v>3.2137327194213898</v>
+        <v>3.15360426902771</v>
       </c>
       <c r="E326">
-        <v>3.1200296878814702</v>
+        <v>3.1129496097564702</v>
       </c>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.2">
@@ -5777,16 +5777,16 @@
         <v>50</v>
       </c>
       <c r="B327">
-        <v>1.7456558301284799</v>
+        <v>1.7359693636359499</v>
       </c>
       <c r="C327">
-        <v>1.6297198534011801</v>
+        <v>1.5969831943512001</v>
       </c>
       <c r="D327">
-        <v>1.59818959236145</v>
+        <v>1.6090121269226101</v>
       </c>
       <c r="E327">
-        <v>1.49997794628143</v>
+        <v>1.5303537845611599</v>
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.2">
@@ -5794,16 +5794,16 @@
         <v>51</v>
       </c>
       <c r="B328">
-        <v>1.3940181643003799</v>
+        <v>1.3861783584454099</v>
       </c>
       <c r="C328">
-        <v>1.3455823659896899</v>
+        <v>1.4198255538940401</v>
       </c>
       <c r="D328">
-        <v>1.4588093757629399</v>
+        <v>1.5059674978256199</v>
       </c>
       <c r="E328">
-        <v>1.4614385366439799</v>
+        <v>1.43075740337372</v>
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.2">
@@ -5811,16 +5811,16 @@
         <v>52</v>
       </c>
       <c r="B329">
-        <v>3.1649007021176101</v>
+        <v>3.15033811559179</v>
       </c>
       <c r="C329">
-        <v>2.71909379959106</v>
+        <v>2.8661575317382799</v>
       </c>
       <c r="D329">
-        <v>2.9713053703308101</v>
+        <v>2.9542188644409202</v>
       </c>
       <c r="E329">
-        <v>3.1519131660461399</v>
+        <v>3.1827118396759002</v>
       </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.2">
@@ -5828,16 +5828,16 @@
         <v>53</v>
       </c>
       <c r="B330">
-        <v>3.92291475526511</v>
+        <v>3.8993971431544301</v>
       </c>
       <c r="C330">
-        <v>3.89303421974182</v>
+        <v>3.97963166236877</v>
       </c>
       <c r="D330">
-        <v>3.9414608478546098</v>
+        <v>3.9828629493713401</v>
       </c>
       <c r="E330">
-        <v>3.6326313018798801</v>
+        <v>3.5849528312683101</v>
       </c>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.2">
@@ -5854,7 +5854,7 @@
         <v>0</v>
       </c>
       <c r="E331">
-        <v>1.33544969558716</v>
+        <v>1.3285204172134399</v>
       </c>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.2">
@@ -5862,16 +5862,16 @@
         <v>55</v>
       </c>
       <c r="B332">
-        <v>4.3984220242315599</v>
+        <v>4.3337593288762397</v>
       </c>
       <c r="C332">
-        <v>2.7823109626770002</v>
+        <v>2.6964583396911599</v>
       </c>
       <c r="D332">
-        <v>5.4174246788024902</v>
+        <v>5.3415484428405797</v>
       </c>
       <c r="E332">
-        <v>7.1670503616332999</v>
+        <v>6.9350886344909703</v>
       </c>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.2">
@@ -5879,7 +5879,7 @@
         <v>56</v>
       </c>
       <c r="B333">
-        <v>2.6873720623427699E-2</v>
+        <v>9.1713294805480603E-3</v>
       </c>
       <c r="C333">
         <v>0</v>
@@ -5888,7 +5888,7 @@
         <v>0</v>
       </c>
       <c r="E333">
-        <v>1.0591677427291899</v>
+        <v>1.00537598133087</v>
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.2">
@@ -5896,16 +5896,16 @@
         <v>57</v>
       </c>
       <c r="B334">
-        <v>8.6134652887256706</v>
+        <v>8.5573870912686107</v>
       </c>
       <c r="C334">
-        <v>4.9970130920410201</v>
+        <v>5.1525111198425302</v>
       </c>
       <c r="D334">
-        <v>7.46496534347534</v>
+        <v>7.4164414405822798</v>
       </c>
       <c r="E334">
-        <v>8.7272176742553693</v>
+        <v>9.0806121826171893</v>
       </c>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.2">
@@ -5913,16 +5913,16 @@
         <v>58</v>
       </c>
       <c r="B335">
-        <v>3.5961803777964103E-2</v>
+        <v>3.5832209220623197E-2</v>
       </c>
       <c r="C335">
         <v>0</v>
       </c>
       <c r="D335">
-        <v>3.8458008319139501E-2</v>
+        <v>3.4477274864911998E-2</v>
       </c>
       <c r="E335">
-        <v>0.133353412151337</v>
+        <v>0.145442575216293</v>
       </c>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.2">
@@ -5930,16 +5930,16 @@
         <v>59</v>
       </c>
       <c r="B336">
-        <v>9.7179422984317902</v>
+        <v>9.6923997279418597</v>
       </c>
       <c r="C336">
-        <v>9.5809297561645508</v>
+        <v>9.7343301773071307</v>
       </c>
       <c r="D336">
-        <v>9.1346111297607404</v>
+        <v>9.0432033538818395</v>
       </c>
       <c r="E336">
-        <v>8.3309793472290004</v>
+        <v>7.9133715629577601</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.2">
@@ -5947,16 +5947,16 @@
         <v>60</v>
       </c>
       <c r="B337">
-        <v>0.32240055845550297</v>
+        <v>0.31880622864993202</v>
       </c>
       <c r="C337">
         <v>0</v>
       </c>
       <c r="D337">
-        <v>0.19388593733310699</v>
+        <v>0.190114200115204</v>
       </c>
       <c r="E337">
-        <v>0.35264739394187899</v>
+        <v>0.35715585947036699</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.2">
@@ -5964,16 +5964,16 @@
         <v>61</v>
       </c>
       <c r="B338">
-        <v>0.32624924847468401</v>
+        <v>0.32668803254978501</v>
       </c>
       <c r="C338">
         <v>0</v>
       </c>
       <c r="D338">
-        <v>0.56807702779769897</v>
+        <v>0.513683080673218</v>
       </c>
       <c r="E338">
-        <v>1.2634369134903001</v>
+        <v>1.1353505849838299</v>
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.2">
@@ -6003,16 +6003,16 @@
         <v>36</v>
       </c>
       <c r="B342">
-        <v>6.25083801387997</v>
+        <v>13.851231817671801</v>
       </c>
       <c r="C342">
-        <v>5.1605153083801296</v>
+        <v>13.663765907287599</v>
       </c>
       <c r="D342">
-        <v>6.4541783332824698</v>
+        <v>14.256072044372599</v>
       </c>
       <c r="E342">
-        <v>7.3791689872741699</v>
+        <v>14.2960710525513</v>
       </c>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.2">
@@ -6020,16 +6020,16 @@
         <v>37</v>
       </c>
       <c r="B343">
-        <v>0.55310093024669904</v>
+        <v>3.9246276025619999</v>
       </c>
       <c r="C343">
-        <v>0</v>
+        <v>3.9512529373168901</v>
       </c>
       <c r="D343">
-        <v>0.55100941658019997</v>
+        <v>4.3528032302856401</v>
       </c>
       <c r="E343">
-        <v>0.89438629150390603</v>
+        <v>4.79412889480591</v>
       </c>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.2">
@@ -6037,16 +6037,16 @@
         <v>38</v>
       </c>
       <c r="B344">
-        <v>0.78250739147773796</v>
+        <v>2.1144580836567699</v>
       </c>
       <c r="C344">
-        <v>0.75093531608581499</v>
+        <v>2.14541411399841</v>
       </c>
       <c r="D344">
-        <v>0.80472230911254905</v>
+        <v>2.1892626285553001</v>
       </c>
       <c r="E344">
-        <v>0.873462975025177</v>
+        <v>2.1225755214691202</v>
       </c>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.2">
@@ -6054,16 +6054,16 @@
         <v>39</v>
       </c>
       <c r="B345">
-        <v>1.4398651056625</v>
+        <v>2.6850210401310002</v>
       </c>
       <c r="C345">
-        <v>1.10470902919769</v>
+        <v>2.4331250190734899</v>
       </c>
       <c r="D345">
-        <v>1.44994640350342</v>
+        <v>2.75194239616394</v>
       </c>
       <c r="E345">
-        <v>1.81253826618195</v>
+        <v>2.8099277019500701</v>
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.2">
@@ -6071,16 +6071,16 @@
         <v>40</v>
       </c>
       <c r="B346">
-        <v>0</v>
+        <v>7.5342222350924297</v>
       </c>
       <c r="C346">
-        <v>0</v>
+        <v>8.0261955261230504</v>
       </c>
       <c r="D346">
-        <v>0</v>
+        <v>8.1251001358032209</v>
       </c>
       <c r="E346">
-        <v>0.81465822458267201</v>
+        <v>8.3748311996459996</v>
       </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.2">
@@ -6088,16 +6088,16 @@
         <v>41</v>
       </c>
       <c r="B347">
-        <v>0.34435475759366402</v>
+        <v>9.3193117427597394E-2</v>
       </c>
       <c r="C347">
-        <v>0.153939694166183</v>
+        <v>4.72988039255142E-2</v>
       </c>
       <c r="D347">
-        <v>0.31565189361572299</v>
+        <v>0.111315324902534</v>
       </c>
       <c r="E347">
-        <v>0.49675178527831998</v>
+        <v>0.473394095897675</v>
       </c>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.2">
@@ -6105,16 +6105,16 @@
         <v>42</v>
       </c>
       <c r="B348">
-        <v>0.95849782715326104</v>
+        <v>0.96950739600263203</v>
       </c>
       <c r="C348">
-        <v>0.75456058979034402</v>
+        <v>0.77218449115753196</v>
       </c>
       <c r="D348">
-        <v>0.93894523382186901</v>
+        <v>0.97676849365234397</v>
       </c>
       <c r="E348">
-        <v>1.04488849639893</v>
+        <v>1.0553939342498799</v>
       </c>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.2">
@@ -6122,16 +6122,16 @@
         <v>43</v>
       </c>
       <c r="B349">
-        <v>0.50616460919091899</v>
+        <v>0.47631583624606799</v>
       </c>
       <c r="C349">
-        <v>0.47394713759422302</v>
+        <v>0.42012476921081499</v>
       </c>
       <c r="D349">
-        <v>0.50259763002395597</v>
+        <v>0.47688087821006803</v>
       </c>
       <c r="E349">
-        <v>0.50363236665725697</v>
+        <v>0.51610565185546897</v>
       </c>
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.2">
@@ -6139,16 +6139,16 @@
         <v>44</v>
       </c>
       <c r="B350">
-        <v>1.7297072723237701</v>
+        <v>1.0129813619319199</v>
       </c>
       <c r="C350">
-        <v>1.5904514789581301</v>
+        <v>0.81663125753402699</v>
       </c>
       <c r="D350">
-        <v>1.72012710571289</v>
+        <v>1.02191162109375</v>
       </c>
       <c r="E350">
-        <v>1.75461030006409</v>
+        <v>1.21887254714966</v>
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.2">
@@ -6156,16 +6156,16 @@
         <v>45</v>
       </c>
       <c r="B351">
-        <v>2.9163654636888898</v>
+        <v>4.5815545558252397</v>
       </c>
       <c r="C351">
-        <v>1.9384630918502801</v>
+        <v>4.2928524017334002</v>
       </c>
       <c r="D351">
-        <v>2.8940997123718302</v>
+        <v>4.6715674400329599</v>
       </c>
       <c r="E351">
-        <v>2.7154004573821999</v>
+        <v>4.7097315788268999</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.2">
@@ -6173,16 +6173,16 @@
         <v>46</v>
       </c>
       <c r="B352">
-        <v>3.5477628233074001</v>
+        <v>7.1345186799735902</v>
       </c>
       <c r="C352">
-        <v>3.5800733566284202</v>
+        <v>8.5860061645507795</v>
       </c>
       <c r="D352">
-        <v>3.5409564971923801</v>
+        <v>7.5543045997619602</v>
       </c>
       <c r="E352">
-        <v>3.5322926044464098</v>
+        <v>6.7644505500793501</v>
       </c>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.2">
@@ -6190,16 +6190,16 @@
         <v>47</v>
       </c>
       <c r="B353">
-        <v>4.5548999707759802E-2</v>
+        <v>0.50116227345615805</v>
       </c>
       <c r="C353">
-        <v>0</v>
+        <v>1.41222085803747E-2</v>
       </c>
       <c r="D353">
-        <v>4.3569546192884397E-2</v>
+        <v>0.47368445992469799</v>
       </c>
       <c r="E353">
-        <v>1.10350942611694</v>
+        <v>0.66282403469085704</v>
       </c>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.2">
@@ -6207,16 +6207,16 @@
         <v>48</v>
       </c>
       <c r="B354">
-        <v>0.99297317801724105</v>
+        <v>0.373426476988305</v>
       </c>
       <c r="C354">
-        <v>0.80765646696090698</v>
+        <v>0</v>
       </c>
       <c r="D354">
-        <v>1.0109286308288601</v>
+        <v>0.35934478044509899</v>
       </c>
       <c r="E354">
-        <v>1.8609799146652199</v>
+        <v>0.65224474668502797</v>
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.2">
@@ -6224,16 +6224,16 @@
         <v>49</v>
       </c>
       <c r="B355">
-        <v>3.2201639169649701</v>
+        <v>0</v>
       </c>
       <c r="C355">
-        <v>2.6617784500122101</v>
+        <v>0</v>
       </c>
       <c r="D355">
-        <v>3.2767190933227499</v>
+        <v>0</v>
       </c>
       <c r="E355">
-        <v>3.4314942359924299</v>
+        <v>0.15743096172809601</v>
       </c>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.2">
@@ -6241,16 +6241,16 @@
         <v>50</v>
       </c>
       <c r="B356">
-        <v>2.1362671931149002</v>
+        <v>0.71108693096561204</v>
       </c>
       <c r="C356">
-        <v>2.2284381389617902</v>
+        <v>0.68912631273269698</v>
       </c>
       <c r="D356">
-        <v>2.1301929950714098</v>
+        <v>0.75810265541076705</v>
       </c>
       <c r="E356">
-        <v>2.1560611724853498</v>
+        <v>0.80192112922668501</v>
       </c>
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.2">
@@ -6258,16 +6258,16 @@
         <v>51</v>
       </c>
       <c r="B357">
-        <v>3.4355310184465799</v>
+        <v>3.4472606831907102</v>
       </c>
       <c r="C357">
-        <v>3.5982758998870898</v>
+        <v>4.06864213943481</v>
       </c>
       <c r="D357">
-        <v>3.4658052921295202</v>
+        <v>3.6101624965667698</v>
       </c>
       <c r="E357">
-        <v>3.1086618900299099</v>
+        <v>3.2994005680084202</v>
       </c>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.2">
@@ -6275,16 +6275,16 @@
         <v>52</v>
       </c>
       <c r="B358">
-        <v>4.4984102392398198</v>
+        <v>2.1428957215447002</v>
       </c>
       <c r="C358">
-        <v>4.3266520500183097</v>
+        <v>2.2043719291686998</v>
       </c>
       <c r="D358">
-        <v>4.4884300231933603</v>
+        <v>2.2173209190368701</v>
       </c>
       <c r="E358">
-        <v>4.2409095764160201</v>
+        <v>2.39706158638</v>
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.2">
@@ -6292,16 +6292,16 @@
         <v>53</v>
       </c>
       <c r="B359">
-        <v>8.7093874327221208</v>
+        <v>6.9050321976336297</v>
       </c>
       <c r="C359">
-        <v>9.3663549423217791</v>
+        <v>8.0368204116821307</v>
       </c>
       <c r="D359">
-        <v>8.7637157440185494</v>
+        <v>7.26505470275879</v>
       </c>
       <c r="E359">
-        <v>7.8117794990539604</v>
+        <v>6.7303919792175302</v>
       </c>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.2">
@@ -6309,16 +6309,16 @@
         <v>54</v>
       </c>
       <c r="B360">
-        <v>12.7450803121731</v>
+        <v>8.5546487691613304</v>
       </c>
       <c r="C360">
-        <v>14.4419612884521</v>
+        <v>9.7906742095947301</v>
       </c>
       <c r="D360">
-        <v>12.7654829025269</v>
+        <v>9.2591171264648402</v>
       </c>
       <c r="E360">
-        <v>11.823371887206999</v>
+        <v>9.0644931793212908</v>
       </c>
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.2">
@@ -6326,16 +6326,16 @@
         <v>55</v>
       </c>
       <c r="B361">
-        <v>27.527113885032499</v>
+        <v>24.130240847265402</v>
       </c>
       <c r="C361">
-        <v>30.709703445434599</v>
+        <v>27.1875610351563</v>
       </c>
       <c r="D361">
-        <v>27.851528167724599</v>
+        <v>25.749778747558601</v>
       </c>
       <c r="E361">
-        <v>26.239387512206999</v>
+        <v>23.723554611206101</v>
       </c>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.2">
@@ -6343,16 +6343,16 @@
         <v>56</v>
       </c>
       <c r="B362">
-        <v>1.46038416991166</v>
+        <v>0</v>
       </c>
       <c r="C362">
-        <v>1.18865430355072</v>
+        <v>0</v>
       </c>
       <c r="D362">
-        <v>1.40445268154144</v>
+        <v>0</v>
       </c>
       <c r="E362">
-        <v>2.0493462085723899</v>
+        <v>5.2801009267568602E-2</v>
       </c>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.2">
@@ -6360,16 +6360,16 @@
         <v>57</v>
       </c>
       <c r="B363">
-        <v>15.672992941573099</v>
+        <v>2.9655142507976699</v>
       </c>
       <c r="C363">
-        <v>15.1523704528809</v>
+        <v>2.36926937103271</v>
       </c>
       <c r="D363">
-        <v>15.538912773132299</v>
+        <v>3.2188484668731698</v>
       </c>
       <c r="E363">
-        <v>14.0390005111694</v>
+        <v>3.94524049758911</v>
       </c>
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.2">
@@ -6377,16 +6377,16 @@
         <v>58</v>
       </c>
       <c r="B364">
-        <v>4.3605088357839002E-2</v>
+        <v>0.20951590296075701</v>
       </c>
       <c r="C364">
-        <v>1.05559481307864E-2</v>
+        <v>0.188750430941582</v>
       </c>
       <c r="D364">
-        <v>4.3405018746852903E-2</v>
+        <v>0.247487217187881</v>
       </c>
       <c r="E364">
-        <v>7.5856603682041196E-2</v>
+        <v>0.31325554847717302</v>
       </c>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.2">
@@ -6394,16 +6394,16 @@
         <v>59</v>
       </c>
       <c r="B365">
-        <v>3.7371695702227599E-2</v>
+        <v>0</v>
       </c>
       <c r="C365">
         <v>0</v>
       </c>
       <c r="D365">
-        <v>3.1325284391641603E-2</v>
+        <v>0</v>
       </c>
       <c r="E365">
-        <v>0.111768931150436</v>
+        <v>0.35285517573356601</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.2">
@@ -6411,16 +6411,16 @@
         <v>60</v>
       </c>
       <c r="B366">
-        <v>1.4842261595453101E-2</v>
+        <v>0</v>
       </c>
       <c r="C366">
         <v>0</v>
       </c>
       <c r="D366">
-        <v>0</v>
+        <v>5.4473146796226501E-2</v>
       </c>
       <c r="E366">
-        <v>1.6393357887864099E-2</v>
+        <v>0.140106841921806</v>
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.2">
@@ -6428,16 +6428,16 @@
         <v>61</v>
       </c>
       <c r="B367">
-        <v>0</v>
+        <v>0.300638970566738</v>
       </c>
       <c r="C367">
-        <v>0</v>
+        <v>0.29581806063652</v>
       </c>
       <c r="D367">
-        <v>1.32890027016401E-2</v>
+        <v>0.29869082570076</v>
       </c>
       <c r="E367">
-        <v>0.10969348251819599</v>
+        <v>0.57093715667724598</v>
       </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.2">
@@ -6467,16 +6467,16 @@
         <v>36</v>
       </c>
       <c r="B371">
-        <v>2.1476488603678798</v>
+        <v>2.21766724847018</v>
       </c>
       <c r="C371">
-        <v>2.0345690250396702</v>
+        <v>1.7671806812286399</v>
       </c>
       <c r="D371">
-        <v>5.0732069015502903</v>
+        <v>4.8098273277282697</v>
       </c>
       <c r="E371">
-        <v>5.7599468231201199</v>
+        <v>5.8797974586486799</v>
       </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.2">
@@ -6484,16 +6484,16 @@
         <v>37</v>
       </c>
       <c r="B372">
-        <v>9.1695025425186003</v>
+        <v>9.1597040108350694</v>
       </c>
       <c r="C372">
-        <v>10.6241397857666</v>
+        <v>10.9095373153687</v>
       </c>
       <c r="D372">
-        <v>8.3523654937744105</v>
+        <v>8.4098968505859393</v>
       </c>
       <c r="E372">
-        <v>7.49226999282837</v>
+        <v>7.6570339202880904</v>
       </c>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.2">
@@ -6501,16 +6501,16 @@
         <v>38</v>
       </c>
       <c r="B373">
-        <v>0.373665236822531</v>
+        <v>0.38657943295428998</v>
       </c>
       <c r="C373">
-        <v>0.29434919357299799</v>
+        <v>0.30848708748817399</v>
       </c>
       <c r="D373">
-        <v>0.80822139978408802</v>
+        <v>0.76784509420394897</v>
       </c>
       <c r="E373">
-        <v>0.92138028144836404</v>
+        <v>0.91444933414459195</v>
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.2">
@@ -6518,16 +6518,16 @@
         <v>39</v>
       </c>
       <c r="B374">
-        <v>0.35182114220968702</v>
+        <v>0.37058838435684999</v>
       </c>
       <c r="C374">
-        <v>0.32052290439605702</v>
+        <v>0.27148005366325401</v>
       </c>
       <c r="D374">
-        <v>0.80078256130218495</v>
+        <v>0.78231567144393899</v>
       </c>
       <c r="E374">
-        <v>1.0867224931716899</v>
+        <v>1.12441861629486</v>
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.2">
@@ -6535,16 +6535,16 @@
         <v>40</v>
       </c>
       <c r="B375">
-        <v>5.7156462931548004</v>
+        <v>5.7556990062090296</v>
       </c>
       <c r="C375">
-        <v>6.7697839736938503</v>
+        <v>6.9157657623290998</v>
       </c>
       <c r="D375">
-        <v>6.74945020675659</v>
+        <v>6.6924209594726598</v>
       </c>
       <c r="E375">
-        <v>6.4200992584228498</v>
+        <v>6.3959379196167001</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.2">
@@ -6552,16 +6552,16 @@
         <v>41</v>
       </c>
       <c r="B376">
-        <v>0.412259043559004</v>
+        <v>0.412786712476642</v>
       </c>
       <c r="C376">
         <v>0</v>
       </c>
       <c r="D376">
-        <v>0.20790188014507299</v>
+        <v>0.22278420627117199</v>
       </c>
       <c r="E376">
-        <v>0.40443679690361001</v>
+        <v>0.40735810995101901</v>
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.2">
@@ -6569,16 +6569,16 @@
         <v>42</v>
       </c>
       <c r="B377">
-        <v>0</v>
+        <v>7.2611714232150701E-3</v>
       </c>
       <c r="C377">
         <v>0</v>
       </c>
       <c r="D377">
-        <v>0.122278049588203</v>
+        <v>0.11539564281702</v>
       </c>
       <c r="E377">
-        <v>0.35360205173492398</v>
+        <v>0.36736837029457098</v>
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.2">
@@ -6586,16 +6586,16 @@
         <v>43</v>
       </c>
       <c r="B378">
-        <v>7.7118144620820202E-3</v>
+        <v>1.07760646924867E-2</v>
       </c>
       <c r="C378">
         <v>0</v>
       </c>
       <c r="D378">
-        <v>5.6895416229963303E-2</v>
+        <v>5.4336465895175899E-2</v>
       </c>
       <c r="E378">
-        <v>0.13514541089534801</v>
+        <v>0.14771994948387099</v>
       </c>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.2">
@@ -6603,16 +6603,16 @@
         <v>44</v>
       </c>
       <c r="B379">
-        <v>3.4655308759015901E-2</v>
+        <v>4.0100177046920898E-2</v>
       </c>
       <c r="C379">
         <v>0</v>
       </c>
       <c r="D379">
-        <v>4.4294413179159199E-2</v>
+        <v>4.1606403887271902E-2</v>
       </c>
       <c r="E379">
-        <v>0.271076619625092</v>
+        <v>0.336325913667679</v>
       </c>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.2">
@@ -6620,16 +6620,16 @@
         <v>45</v>
       </c>
       <c r="B380">
-        <v>0.472011904838748</v>
+        <v>0.47624107576458102</v>
       </c>
       <c r="C380">
         <v>0</v>
       </c>
       <c r="D380">
-        <v>1.5439350605011</v>
+        <v>1.47591829299927</v>
       </c>
       <c r="E380">
-        <v>2.1518473625183101</v>
+        <v>1.98203337192535</v>
       </c>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.2">
@@ -6637,16 +6637,16 @@
         <v>46</v>
       </c>
       <c r="B381">
-        <v>2.2244505357734599</v>
+        <v>2.2303149815730001</v>
       </c>
       <c r="C381">
-        <v>1.9324153661727901</v>
+        <v>1.8668081760406501</v>
       </c>
       <c r="D381">
-        <v>3.9653584957122798</v>
+        <v>3.8016324043273899</v>
       </c>
       <c r="E381">
-        <v>3.9410493373870898</v>
+        <v>3.7746396064758301</v>
       </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.2">
@@ -6654,16 +6654,16 @@
         <v>47</v>
       </c>
       <c r="B382">
-        <v>1.03441050505432</v>
+        <v>1.03927109216959</v>
       </c>
       <c r="C382">
-        <v>0.35872679948806802</v>
+        <v>0.240465462207794</v>
       </c>
       <c r="D382">
-        <v>0.87344950437545799</v>
+        <v>0.89309072494506803</v>
       </c>
       <c r="E382">
-        <v>0.99811422824859597</v>
+        <v>1.0190001726150499</v>
       </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.2">
@@ -6671,16 +6671,16 @@
         <v>48</v>
       </c>
       <c r="B383">
-        <v>1.19206620557281</v>
+        <v>1.19457348933908</v>
       </c>
       <c r="C383">
         <v>0</v>
       </c>
       <c r="D383">
-        <v>0.83250886201858498</v>
+        <v>0.83147996664047197</v>
       </c>
       <c r="E383">
-        <v>1.09188640117645</v>
+        <v>1.0241347551345801</v>
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.2">
@@ -6688,16 +6688,16 @@
         <v>49</v>
       </c>
       <c r="B384">
-        <v>0.87447776993837201</v>
+        <v>0.86601675754950602</v>
       </c>
       <c r="C384">
         <v>0</v>
       </c>
       <c r="D384">
-        <v>0.10056430101394701</v>
+        <v>0.22165136039257</v>
       </c>
       <c r="E384">
-        <v>0.92153424024581898</v>
+        <v>0.87038171291351296</v>
       </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.2">
@@ -6705,16 +6705,16 @@
         <v>50</v>
       </c>
       <c r="B385">
-        <v>0.82709422371766705</v>
+        <v>0.82252424278663505</v>
       </c>
       <c r="C385">
-        <v>0.35183739662170399</v>
+        <v>0.33828490972518899</v>
       </c>
       <c r="D385">
-        <v>0.58978790044784501</v>
+        <v>0.60303169488906905</v>
       </c>
       <c r="E385">
-        <v>0.74526202678680398</v>
+        <v>0.73118531703948997</v>
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.2">
@@ -6722,16 +6722,16 @@
         <v>51</v>
       </c>
       <c r="B386">
-        <v>1.04550622449105</v>
+        <v>1.04642833648359</v>
       </c>
       <c r="C386">
-        <v>1.06878066062927</v>
+        <v>1.01692295074463</v>
       </c>
       <c r="D386">
-        <v>1.6082521677017201</v>
+        <v>1.5481314659118699</v>
       </c>
       <c r="E386">
-        <v>1.5703806877136199</v>
+        <v>1.50795781612396</v>
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.2">
@@ -6748,7 +6748,7 @@
         <v>0</v>
       </c>
       <c r="E387">
-        <v>0.27130311727523798</v>
+        <v>0.21085786819457999</v>
       </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.2">
@@ -6756,16 +6756,16 @@
         <v>53</v>
       </c>
       <c r="B388">
-        <v>3.05942754451705</v>
+        <v>3.0520254554855799</v>
       </c>
       <c r="C388">
-        <v>3.6533100605011</v>
+        <v>3.4837491512298602</v>
       </c>
       <c r="D388">
-        <v>3.68855857849121</v>
+        <v>3.5864171981811501</v>
       </c>
       <c r="E388">
-        <v>3.49090576171875</v>
+        <v>3.3025460243225102</v>
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.2">
@@ -6773,16 +6773,16 @@
         <v>54</v>
       </c>
       <c r="B389">
-        <v>13.393980627892899</v>
+        <v>13.332083312568001</v>
       </c>
       <c r="C389">
-        <v>14.6627607345581</v>
+        <v>14.523455619811999</v>
       </c>
       <c r="D389">
-        <v>12.2554111480713</v>
+        <v>12.2293615341187</v>
       </c>
       <c r="E389">
-        <v>10.4862575531006</v>
+        <v>10.3512935638428</v>
       </c>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.2">
@@ -6790,16 +6790,16 @@
         <v>55</v>
       </c>
       <c r="B390">
-        <v>27.732544675661</v>
+        <v>27.6200999410467</v>
       </c>
       <c r="C390">
-        <v>32.4480171203613</v>
+        <v>30.653444290161101</v>
       </c>
       <c r="D390">
-        <v>26.928045272827099</v>
+        <v>26.925695419311499</v>
       </c>
       <c r="E390">
-        <v>22.631273269653299</v>
+        <v>22.579818725585898</v>
       </c>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.2">
@@ -6807,16 +6807,16 @@
         <v>56</v>
       </c>
       <c r="B391">
-        <v>4.8220066981717702</v>
+        <v>4.7907456015738301</v>
       </c>
       <c r="C391">
-        <v>3.1040329933166499</v>
+        <v>3.23297166824341</v>
       </c>
       <c r="D391">
-        <v>3.5254392623901398</v>
+        <v>3.7802324295043901</v>
       </c>
       <c r="E391">
-        <v>4.8447198867797896</v>
+        <v>4.8734722137451199</v>
       </c>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.2">
@@ -6824,16 +6824,16 @@
         <v>57</v>
       </c>
       <c r="B392">
-        <v>4.1027146251207496</v>
+        <v>4.0599223260047701</v>
       </c>
       <c r="C392">
-        <v>1.341224193573</v>
+        <v>1.61036348342896</v>
       </c>
       <c r="D392">
-        <v>2.38896608352661</v>
+        <v>2.5004119873046902</v>
       </c>
       <c r="E392">
-        <v>3.5156431198120099</v>
+        <v>3.45236444473267</v>
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.2">
@@ -6841,16 +6841,16 @@
         <v>58</v>
       </c>
       <c r="B393">
-        <v>0.210538864199144</v>
+        <v>0.209932760618257</v>
       </c>
       <c r="C393">
-        <v>0.14968846738338501</v>
+        <v>0.159928679466248</v>
       </c>
       <c r="D393">
-        <v>0.22391213476657901</v>
+        <v>0.22204527258873</v>
       </c>
       <c r="E393">
-        <v>0.279779672622681</v>
+        <v>0.270303815603256</v>
       </c>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.2">
@@ -6858,16 +6858,16 @@
         <v>59</v>
       </c>
       <c r="B394">
-        <v>14.1726106788013</v>
+        <v>14.1389890756393</v>
       </c>
       <c r="C394">
-        <v>11.5036373138428</v>
+        <v>12.730542182922401</v>
       </c>
       <c r="D394">
-        <v>10.9239358901978</v>
+        <v>11.132320404052701</v>
       </c>
       <c r="E394">
-        <v>11.814094543456999</v>
+        <v>12.190637588501</v>
       </c>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.2">
@@ -6884,7 +6884,7 @@
         <v>0</v>
       </c>
       <c r="E395">
-        <v>5.5371388792991597E-2</v>
+        <v>6.7934326827526106E-2</v>
       </c>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.2">
@@ -6892,16 +6892,16 @@
         <v>61</v>
       </c>
       <c r="B396">
-        <v>10.184905597755201</v>
+        <v>10.1495607039053</v>
       </c>
       <c r="C396">
-        <v>9.3822088241577095</v>
+        <v>9.9706077575683594</v>
       </c>
       <c r="D396">
-        <v>8.33648681640625</v>
+        <v>8.3521537780761701</v>
       </c>
       <c r="E396">
-        <v>8.3458976745605504</v>
+        <v>8.5610313415527308</v>
       </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.2">
@@ -6931,16 +6931,16 @@
         <v>36</v>
       </c>
       <c r="B400">
-        <v>13.8580180764473</v>
+        <v>6.2524458173419202</v>
       </c>
       <c r="C400">
-        <v>13.551267623901399</v>
+        <v>4.8720345497131303</v>
       </c>
       <c r="D400">
-        <v>14.304704666137701</v>
+        <v>6.45420169830322</v>
       </c>
       <c r="E400">
-        <v>14.1132040023804</v>
+        <v>7.17718553543091</v>
       </c>
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.2">
@@ -6948,16 +6948,16 @@
         <v>37</v>
       </c>
       <c r="B401">
-        <v>3.9267821558385401</v>
+        <v>0.553654266964411</v>
       </c>
       <c r="C401">
-        <v>4.0427699089050302</v>
+        <v>0</v>
       </c>
       <c r="D401">
-        <v>4.3809304237365696</v>
+        <v>0.56327891349792503</v>
       </c>
       <c r="E401">
-        <v>4.7180404663085902</v>
+        <v>0.85657370090484597</v>
       </c>
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.2">
@@ -6965,16 +6965,16 @@
         <v>38</v>
       </c>
       <c r="B402">
-        <v>2.1154500601610402</v>
+        <v>0.782684213272685</v>
       </c>
       <c r="C402">
-        <v>2.1401112079620401</v>
+        <v>0.72655713558196999</v>
       </c>
       <c r="D402">
-        <v>2.2054955959320099</v>
+        <v>0.79637217521667503</v>
       </c>
       <c r="E402">
-        <v>2.0929772853851301</v>
+        <v>0.86940008401870705</v>
       </c>
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.2">
@@ -6982,16 +6982,16 @@
         <v>39</v>
       </c>
       <c r="B403">
-        <v>2.6861080300584002</v>
+        <v>1.44024357468493</v>
       </c>
       <c r="C403">
-        <v>2.4614002704620401</v>
+        <v>1.1209802627563501</v>
       </c>
       <c r="D403">
-        <v>2.7734017372131299</v>
+        <v>1.4590915441513099</v>
       </c>
       <c r="E403">
-        <v>2.8221204280853298</v>
+        <v>1.8240045309066799</v>
       </c>
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.2">
@@ -6999,16 +6999,16 @@
         <v>40</v>
       </c>
       <c r="B404">
-        <v>7.5382187862519796</v>
+        <v>0</v>
       </c>
       <c r="C404">
-        <v>8.0743360519409197</v>
+        <v>0</v>
       </c>
       <c r="D404">
-        <v>8.0923433303833008</v>
+        <v>0</v>
       </c>
       <c r="E404">
-        <v>8.4790077209472692</v>
+        <v>0.97891449928283703</v>
       </c>
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.2">
@@ -7016,16 +7016,16 @@
         <v>41</v>
       </c>
       <c r="B405">
-        <v>9.2601600204533896E-2</v>
+        <v>0.34464598440966598</v>
       </c>
       <c r="C405">
-        <v>4.6499915421009098E-2</v>
+        <v>0.16297054290771501</v>
       </c>
       <c r="D405">
-        <v>0.107636600732803</v>
+        <v>0.29823204874992398</v>
       </c>
       <c r="E405">
-        <v>0.49428641796112099</v>
+        <v>0.50022959709167503</v>
       </c>
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.2">
@@ -7033,16 +7033,16 @@
         <v>42</v>
       </c>
       <c r="B406">
-        <v>0.96978057632777004</v>
+        <v>0.95877023204054901</v>
       </c>
       <c r="C406">
-        <v>0.81125336885452304</v>
+        <v>0.75949972867965698</v>
       </c>
       <c r="D406">
-        <v>0.96360182762145996</v>
+        <v>0.93619221448898304</v>
       </c>
       <c r="E406">
-        <v>1.04055607318878</v>
+        <v>1.0487477779388401</v>
       </c>
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.2">
@@ -7050,16 +7050,16 @@
         <v>43</v>
       </c>
       <c r="B407">
-        <v>0.47651258006335401</v>
+        <v>0.50632113015139102</v>
       </c>
       <c r="C407">
-        <v>0.416803479194641</v>
+        <v>0.477222830057144</v>
       </c>
       <c r="D407">
-        <v>0.473544001579285</v>
+        <v>0.50256383419036899</v>
       </c>
       <c r="E407">
-        <v>0.51777762174606301</v>
+        <v>0.50411200523376498</v>
       </c>
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.2">
@@ -7067,16 +7067,16 @@
         <v>44</v>
       </c>
       <c r="B408">
-        <v>1.0136310758214899</v>
+        <v>1.7302750502549</v>
       </c>
       <c r="C408">
-        <v>0.850397169589996</v>
+        <v>1.58908915519714</v>
       </c>
       <c r="D408">
-        <v>1.0250481367111199</v>
+        <v>1.71359431743622</v>
       </c>
       <c r="E408">
-        <v>1.23046779632568</v>
+        <v>1.76350498199463</v>
       </c>
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.2">
@@ -7084,16 +7084,16 @@
         <v>45</v>
       </c>
       <c r="B409">
-        <v>4.5918432912037597</v>
+        <v>2.92398132410624</v>
       </c>
       <c r="C409">
-        <v>4.2995309829711896</v>
+        <v>2.0622081756591801</v>
       </c>
       <c r="D409">
-        <v>4.7782850265502903</v>
+        <v>2.9219059944152801</v>
       </c>
       <c r="E409">
-        <v>4.7315526008606001</v>
+        <v>2.7088029384613002</v>
       </c>
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.2">
@@ -7101,16 +7101,16 @@
         <v>46</v>
       </c>
       <c r="B410">
-        <v>7.1378073016522503</v>
+        <v>3.5476228227754598</v>
       </c>
       <c r="C410">
-        <v>8.5532255172729492</v>
+        <v>3.5611839294433598</v>
       </c>
       <c r="D410">
-        <v>7.5399518013000497</v>
+        <v>3.5875000953674299</v>
       </c>
       <c r="E410">
-        <v>6.8242125511169398</v>
+        <v>3.5177850723266602</v>
       </c>
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.2">
@@ -7118,16 +7118,16 @@
         <v>47</v>
       </c>
       <c r="B411">
-        <v>0.50102990701738603</v>
+        <v>4.5426311693635903E-2</v>
       </c>
       <c r="C411">
         <v>0</v>
       </c>
       <c r="D411">
-        <v>0.47526884078979498</v>
+        <v>5.5127009749412502E-2</v>
       </c>
       <c r="E411">
-        <v>0.66795831918716397</v>
+        <v>1.0969039201736499</v>
       </c>
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.2">
@@ -7135,16 +7135,16 @@
         <v>48</v>
       </c>
       <c r="B412">
-        <v>0.373316401307072</v>
+        <v>0.99243497640488898</v>
       </c>
       <c r="C412">
-        <v>0</v>
+        <v>0.82527416944503795</v>
       </c>
       <c r="D412">
-        <v>0.33917865157127403</v>
+        <v>1.0315731763839699</v>
       </c>
       <c r="E412">
-        <v>0.68826687335967995</v>
+        <v>1.8260360956192001</v>
       </c>
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.2">
@@ -7152,16 +7152,16 @@
         <v>49</v>
       </c>
       <c r="B413">
-        <v>0</v>
+        <v>3.22147979184725</v>
       </c>
       <c r="C413">
-        <v>0</v>
+        <v>2.6360273361206099</v>
       </c>
       <c r="D413">
-        <v>0</v>
+        <v>3.2626183032989502</v>
       </c>
       <c r="E413">
-        <v>0.142966568470001</v>
+        <v>3.3792796134948699</v>
       </c>
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.2">
@@ -7169,16 +7169,16 @@
         <v>50</v>
       </c>
       <c r="B414">
-        <v>0.71183309204270795</v>
+        <v>2.1367831664137702</v>
       </c>
       <c r="C414">
-        <v>0.681532442569733</v>
+        <v>2.2103645801544198</v>
       </c>
       <c r="D414">
-        <v>0.75970196723937999</v>
+        <v>2.1325421333313002</v>
       </c>
       <c r="E414">
-        <v>0.81932264566421498</v>
+        <v>2.0752704143524201</v>
       </c>
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.2">
@@ -7186,16 +7186,16 @@
         <v>51</v>
       </c>
       <c r="B415">
-        <v>3.4496108158219898</v>
+        <v>3.43608199057081</v>
       </c>
       <c r="C415">
-        <v>4.10359764099121</v>
+        <v>3.5996351242065399</v>
       </c>
       <c r="D415">
-        <v>3.6361517906189</v>
+        <v>3.47450923919678</v>
       </c>
       <c r="E415">
-        <v>3.29681348800659</v>
+        <v>3.0854413509368901</v>
       </c>
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.2">
@@ -7203,16 +7203,16 @@
         <v>52</v>
       </c>
       <c r="B416">
-        <v>2.1451515415294198</v>
+        <v>4.4996010449881201</v>
       </c>
       <c r="C416">
-        <v>2.2067954540252699</v>
+        <v>4.4044327735900897</v>
       </c>
       <c r="D416">
-        <v>2.2496967315673801</v>
+        <v>4.4727034568786603</v>
       </c>
       <c r="E416">
-        <v>2.4020233154296902</v>
+        <v>4.1999320983886701</v>
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.2">
@@ -7220,16 +7220,16 @@
         <v>53</v>
       </c>
       <c r="B417">
-        <v>6.9106783264822997</v>
+        <v>8.7114908662108199</v>
       </c>
       <c r="C417">
-        <v>8.1215791702270508</v>
+        <v>9.3836812973022496</v>
       </c>
       <c r="D417">
-        <v>7.3295545578002903</v>
+        <v>8.7605705261230504</v>
       </c>
       <c r="E417">
-        <v>6.7397651672363299</v>
+        <v>7.7749004364013699</v>
       </c>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.2">
@@ -7237,16 +7237,16 @@
         <v>54</v>
       </c>
       <c r="B418">
-        <v>8.5661707306213799</v>
+        <v>12.7424010466779</v>
       </c>
       <c r="C418">
-        <v>9.7574243545532209</v>
+        <v>14.2632837295532</v>
       </c>
       <c r="D418">
-        <v>9.1777315139770508</v>
+        <v>12.7494163513184</v>
       </c>
       <c r="E418">
-        <v>9.1616106033325195</v>
+        <v>11.7817630767822</v>
       </c>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.2">
@@ -7254,16 +7254,16 @@
         <v>55</v>
       </c>
       <c r="B419">
-        <v>24.149853467092498</v>
+        <v>27.531264184977498</v>
       </c>
       <c r="C419">
-        <v>26.9210529327393</v>
+        <v>30.5793552398682</v>
       </c>
       <c r="D419">
-        <v>25.525411605835</v>
+        <v>27.8304958343506</v>
       </c>
       <c r="E419">
-        <v>23.7469177246094</v>
+        <v>26.433376312255898</v>
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.2">
@@ -7271,16 +7271,16 @@
         <v>56</v>
       </c>
       <c r="B420">
-        <v>0</v>
+        <v>1.46125240011531</v>
       </c>
       <c r="C420">
-        <v>0</v>
+        <v>1.190584897995</v>
       </c>
       <c r="D420">
-        <v>0</v>
+        <v>1.4049046039581301</v>
       </c>
       <c r="E420">
-        <v>0</v>
+        <v>2.12249755859375</v>
       </c>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.2">
@@ -7288,16 +7288,16 @@
         <v>57</v>
       </c>
       <c r="B421">
-        <v>2.9732987279183001</v>
+        <v>15.681105423143901</v>
       </c>
       <c r="C421">
-        <v>2.4893920421600302</v>
+        <v>15.5657243728638</v>
       </c>
       <c r="D421">
-        <v>3.27105665206909</v>
+        <v>15.4898872375488</v>
       </c>
       <c r="E421">
-        <v>3.9941668510436998</v>
+        <v>14.1488447189331</v>
       </c>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.2">
@@ -7305,16 +7305,16 @@
         <v>58</v>
       </c>
       <c r="B422">
-        <v>0.208924287071836</v>
+        <v>4.3502612015673597E-2</v>
       </c>
       <c r="C422">
-        <v>0.19448459148406999</v>
+        <v>9.8956245929002797E-3</v>
       </c>
       <c r="D422">
-        <v>0.23888798058033001</v>
+        <v>4.3712131679058103E-2</v>
       </c>
       <c r="E422">
-        <v>0.31259191036224399</v>
+        <v>7.4376530945301098E-2</v>
       </c>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.2">
@@ -7322,16 +7322,16 @@
         <v>59</v>
       </c>
       <c r="B423">
-        <v>0</v>
+        <v>3.7147653254966599E-2</v>
       </c>
       <c r="C423">
         <v>0</v>
       </c>
       <c r="D423">
-        <v>0</v>
+        <v>3.3458270132541698E-2</v>
       </c>
       <c r="E423">
-        <v>0.242609292268753</v>
+        <v>0.110767990350723</v>
       </c>
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.2">
@@ -7339,16 +7339,16 @@
         <v>60</v>
       </c>
       <c r="B424">
-        <v>0</v>
+        <v>1.51225575341917E-2</v>
       </c>
       <c r="C424">
         <v>0</v>
       </c>
       <c r="D424">
-        <v>5.6013293564319597E-2</v>
+        <v>0</v>
       </c>
       <c r="E424">
-        <v>0.14905089139938399</v>
+        <v>1.8868785351514799E-2</v>
       </c>
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.2">
@@ -7356,16 +7356,16 @@
         <v>61</v>
       </c>
       <c r="B425">
-        <v>0.30219896809812202</v>
+        <v>0</v>
       </c>
       <c r="C425">
-        <v>0.27655065059661899</v>
+        <v>0</v>
       </c>
       <c r="D425">
-        <v>0.29640871286392201</v>
+        <v>2.5545584037899999E-2</v>
       </c>
       <c r="E425">
-        <v>0.57172799110412598</v>
+        <v>0.122473731637001</v>
       </c>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.2">
@@ -7395,16 +7395,16 @@
         <v>36</v>
       </c>
       <c r="B429">
-        <v>13.7958925702735</v>
+        <v>13.8415121407565</v>
       </c>
       <c r="C429">
-        <v>15.4814348220825</v>
+        <v>16.890903472900401</v>
       </c>
       <c r="D429">
-        <v>10.520952224731399</v>
+        <v>10.5702524185181</v>
       </c>
       <c r="E429">
-        <v>8.6760997772216797</v>
+        <v>9.0150690078735405</v>
       </c>
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.2">
@@ -7412,16 +7412,16 @@
         <v>37</v>
       </c>
       <c r="B430">
-        <v>7.7542977638335699</v>
+        <v>7.7664537123531803</v>
       </c>
       <c r="C430">
-        <v>8.5510759353637695</v>
+        <v>7.5585422515869096</v>
       </c>
       <c r="D430">
-        <v>6.6831955909729004</v>
+        <v>6.4947400093078604</v>
       </c>
       <c r="E430">
-        <v>6.0491700172424299</v>
+        <v>5.6438183784484899</v>
       </c>
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.2">
@@ -7429,16 +7429,16 @@
         <v>38</v>
       </c>
       <c r="B431">
-        <v>1.67916497939761</v>
+        <v>1.68357327093919</v>
       </c>
       <c r="C431">
-        <v>1.4303011894226101</v>
+        <v>1.4621938467025799</v>
       </c>
       <c r="D431">
-        <v>1.1907167434692401</v>
+        <v>1.19976353645325</v>
       </c>
       <c r="E431">
-        <v>1.0798591375351001</v>
+        <v>1.0720193386077901</v>
       </c>
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.2">
@@ -7446,16 +7446,16 @@
         <v>39</v>
       </c>
       <c r="B432">
-        <v>1.94508941979209</v>
+        <v>1.9482563876671899</v>
       </c>
       <c r="C432">
-        <v>1.8420661687851001</v>
+        <v>1.8429247140884399</v>
       </c>
       <c r="D432">
-        <v>1.5541343688964799</v>
+        <v>1.58741843700409</v>
       </c>
       <c r="E432">
-        <v>1.55475914478302</v>
+        <v>1.62038922309875</v>
       </c>
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.2">
@@ -7463,16 +7463,16 @@
         <v>40</v>
       </c>
       <c r="B433">
-        <v>12.765959394651</v>
+        <v>12.7855403843188</v>
       </c>
       <c r="C433">
-        <v>12.868069648742701</v>
+        <v>12.8859958648682</v>
       </c>
       <c r="D433">
-        <v>10.394458770751999</v>
+        <v>10.2860107421875</v>
       </c>
       <c r="E433">
-        <v>9.0001897811889595</v>
+        <v>9.16412448883057</v>
       </c>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.2">
@@ -7480,16 +7480,16 @@
         <v>41</v>
       </c>
       <c r="B434">
-        <v>0.18231743376171999</v>
+        <v>0.17861796769024099</v>
       </c>
       <c r="C434">
         <v>0</v>
       </c>
       <c r="D434">
-        <v>0.331501334905624</v>
+        <v>0.29905107617378202</v>
       </c>
       <c r="E434">
-        <v>0.52633047103881803</v>
+        <v>0.51773738861083995</v>
       </c>
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.2">
@@ -7506,7 +7506,7 @@
         <v>0</v>
       </c>
       <c r="E435">
-        <v>0.222769185900688</v>
+        <v>0.24328166246414201</v>
       </c>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.2">
@@ -7523,7 +7523,7 @@
         <v>0</v>
       </c>
       <c r="E436">
-        <v>9.5727868378162398E-2</v>
+        <v>9.5006622374057798E-2</v>
       </c>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.2">
@@ -7531,16 +7531,16 @@
         <v>44</v>
       </c>
       <c r="B437">
-        <v>2.8599057520226098E-3</v>
+        <v>4.0508825026916101E-3</v>
       </c>
       <c r="C437">
         <v>0</v>
       </c>
       <c r="D437">
-        <v>0.19035479426384</v>
+        <v>0.194058611989021</v>
       </c>
       <c r="E437">
-        <v>0.46306177973747298</v>
+        <v>0.49573284387588501</v>
       </c>
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.2">
@@ -7548,16 +7548,16 @@
         <v>45</v>
       </c>
       <c r="B438">
-        <v>4.9964788975354697</v>
+        <v>5.0530204048795202</v>
       </c>
       <c r="C438">
         <v>0</v>
       </c>
       <c r="D438">
-        <v>2.4376513957977299</v>
+        <v>2.62319755554199</v>
       </c>
       <c r="E438">
-        <v>3.7316017150878902</v>
+        <v>3.8757452964782702</v>
       </c>
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.2">
@@ -7565,16 +7565,16 @@
         <v>46</v>
       </c>
       <c r="B439">
-        <v>7.5949923683522602</v>
+        <v>7.6390009121208298</v>
       </c>
       <c r="C439">
         <v>0</v>
       </c>
       <c r="D439">
-        <v>5.2971100807189897</v>
+        <v>5.6074385643005398</v>
       </c>
       <c r="E439">
-        <v>4.7020678520202601</v>
+        <v>4.8332476615905797</v>
       </c>
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.2">
@@ -7582,16 +7582,16 @@
         <v>47</v>
       </c>
       <c r="B440">
-        <v>0.78196741601299502</v>
+        <v>0.78084395174838706</v>
       </c>
       <c r="C440">
-        <v>7.0867821574211107E-2</v>
+        <v>6.5792217850685106E-2</v>
       </c>
       <c r="D440">
-        <v>0.97494935989379905</v>
+        <v>0.93758970499038696</v>
       </c>
       <c r="E440">
-        <v>1.6544338464736901</v>
+        <v>1.5404974222183201</v>
       </c>
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.2">
@@ -7608,7 +7608,7 @@
         <v>0</v>
       </c>
       <c r="E441">
-        <v>1.4700222015380899</v>
+        <v>1.53369188308716</v>
       </c>
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.2">
@@ -7622,10 +7622,10 @@
         <v>0</v>
       </c>
       <c r="D442">
-        <v>0.56261301040649403</v>
+        <v>0.51508933305740401</v>
       </c>
       <c r="E442">
-        <v>1.60816979408264</v>
+        <v>1.40942883491516</v>
       </c>
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.2">
@@ -7633,16 +7633,16 @@
         <v>50</v>
       </c>
       <c r="B443">
-        <v>0.95665949193979904</v>
+        <v>0.96155545821500799</v>
       </c>
       <c r="C443">
-        <v>1.38905012607574</v>
+        <v>1.35311543941498</v>
       </c>
       <c r="D443">
-        <v>1.1215025186538701</v>
+        <v>1.1003597974777199</v>
       </c>
       <c r="E443">
-        <v>1.2192232608795199</v>
+        <v>1.14191317558289</v>
       </c>
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.2">
@@ -7650,16 +7650,16 @@
         <v>51</v>
       </c>
       <c r="B444">
-        <v>3.6388706125731201</v>
+        <v>3.6589766449374599</v>
       </c>
       <c r="C444">
-        <v>2.2176442146301301</v>
+        <v>2.2644526958465598</v>
       </c>
       <c r="D444">
-        <v>2.8623588085174601</v>
+        <v>2.9880235195159899</v>
       </c>
       <c r="E444">
-        <v>2.4382746219635001</v>
+        <v>2.5086543560028098</v>
       </c>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.2">
@@ -7667,16 +7667,16 @@
         <v>52</v>
       </c>
       <c r="B445">
-        <v>0.52378163743314898</v>
+        <v>0.53541679057895197</v>
       </c>
       <c r="C445">
         <v>0</v>
       </c>
       <c r="D445">
-        <v>0.50657951831817605</v>
+        <v>0.55939090251922596</v>
       </c>
       <c r="E445">
-        <v>1.0017685890197801</v>
+        <v>1.05367863178253</v>
       </c>
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.2">
@@ -7684,16 +7684,16 @@
         <v>53</v>
       </c>
       <c r="B446">
-        <v>7.2346857128539801</v>
+        <v>7.2783831064092697</v>
       </c>
       <c r="C446">
-        <v>6.1042380332946804</v>
+        <v>5.8952145576477104</v>
       </c>
       <c r="D446">
-        <v>5.9581985473632804</v>
+        <v>6.21456098556519</v>
       </c>
       <c r="E446">
-        <v>5.2554945945739702</v>
+        <v>5.2558341026306197</v>
       </c>
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.2">
@@ -7701,16 +7701,16 @@
         <v>54</v>
       </c>
       <c r="B447">
-        <v>8.7445745465552296</v>
+        <v>8.7797494860415703</v>
       </c>
       <c r="C447">
-        <v>2.0894522666931201</v>
+        <v>2.14736700057983</v>
       </c>
       <c r="D447">
-        <v>7.6850719451904297</v>
+        <v>7.6019473075866699</v>
       </c>
       <c r="E447">
-        <v>6.6256346702575701</v>
+        <v>6.4919052124023402</v>
       </c>
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.2">
@@ -7718,16 +7718,16 @@
         <v>55</v>
       </c>
       <c r="B448">
-        <v>34.891960553677002</v>
+        <v>35.070225392452798</v>
       </c>
       <c r="C448">
-        <v>40.039443969726598</v>
+        <v>39.643058776855497</v>
       </c>
       <c r="D448">
-        <v>29.5994987487793</v>
+        <v>29.557838439941399</v>
       </c>
       <c r="E448">
-        <v>22.174970626831101</v>
+        <v>21.750097274780298</v>
       </c>
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.2">
@@ -7735,16 +7735,16 @@
         <v>56</v>
       </c>
       <c r="B449">
-        <v>6.9305778312950697</v>
+        <v>6.9496285007558001</v>
       </c>
       <c r="C449">
-        <v>5.3873586654663104</v>
+        <v>5.6284050941467303</v>
       </c>
       <c r="D449">
-        <v>6.95479536056519</v>
+        <v>6.5759463310241699</v>
       </c>
       <c r="E449">
-        <v>6.6461777687072798</v>
+        <v>6.8986115455627397</v>
       </c>
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.2">
@@ -7752,16 +7752,16 @@
         <v>57</v>
       </c>
       <c r="B450">
-        <v>0.16686277092839799</v>
+        <v>0.19364083385481201</v>
       </c>
       <c r="C450">
         <v>0</v>
       </c>
       <c r="D450">
-        <v>1.67505502700806</v>
+        <v>1.7534054517746001</v>
       </c>
       <c r="E450">
-        <v>3.4276752471923801</v>
+        <v>3.4099862575531001</v>
       </c>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.2">
@@ -7769,16 +7769,16 @@
         <v>58</v>
       </c>
       <c r="B451">
-        <v>0.509482675192934</v>
+        <v>0.50978819500876504</v>
       </c>
       <c r="C451">
-        <v>0.192620009183884</v>
+        <v>0.16759228706359899</v>
       </c>
       <c r="D451">
-        <v>0.37991258502006497</v>
+        <v>0.380846947431564</v>
       </c>
       <c r="E451">
-        <v>0.37437245249748202</v>
+        <v>0.35428732633590698</v>
       </c>
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.2">
@@ -7786,16 +7786,16 @@
         <v>59</v>
       </c>
       <c r="B452">
-        <v>1.01601944691324</v>
+        <v>0.99991783084811903</v>
       </c>
       <c r="C452">
         <v>0</v>
       </c>
       <c r="D452">
-        <v>1.4009063243866</v>
+        <v>1.2331268787384</v>
       </c>
       <c r="E452">
-        <v>6.6180148124694798</v>
+        <v>6.6504702568054199</v>
       </c>
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.2">
@@ -7803,16 +7803,16 @@
         <v>60</v>
       </c>
       <c r="B453">
-        <v>1.77853256960892</v>
+        <v>1.78054322635062</v>
       </c>
       <c r="C453">
-        <v>2.3363833427429199</v>
+        <v>2.1944448947906499</v>
       </c>
       <c r="D453">
-        <v>1.7184855937957799</v>
+        <v>1.7199519872665401</v>
       </c>
       <c r="E453">
-        <v>1.96103274822235</v>
+        <v>2.0028417110443102</v>
       </c>
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.2">
@@ -7829,7 +7829,7 @@
         <v>0</v>
       </c>
       <c r="E454">
-        <v>1.42309617996216</v>
+        <v>1.4219326972961399</v>
       </c>
     </row>
   </sheetData>
